--- a/june 2026/LMT Orders.xlsx
+++ b/june 2026/LMT Orders.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989F5443-22A5-4FCD-A8A5-F59D98253FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9B76E-D3EB-44BF-B022-080919B18BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2004,6 +2004,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2038,45 +2077,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2635,13 +2635,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="169">
+      <c r="B1" s="182">
         <v>46186</v>
       </c>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2663,10 +2663,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="179" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2699,13 +2699,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="183"/>
-      <c r="N2" s="184"/>
-      <c r="O2" s="185"/>
-      <c r="P2" s="186" t="s">
+      <c r="M2" s="171"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="187"/>
+      <c r="Q2" s="175"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2724,8 +2724,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="191"/>
-      <c r="B3" s="171"/>
+      <c r="A3" s="179"/>
+      <c r="B3" s="184"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2756,29 +2756,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="188" t="s">
+      <c r="M3" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="189"/>
-      <c r="O3" s="190"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="178"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="173" t="s">
+      <c r="R3" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="175"/>
-      <c r="V3" s="176" t="s">
+      <c r="S3" s="187"/>
+      <c r="T3" s="187"/>
+      <c r="U3" s="188"/>
+      <c r="V3" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="177"/>
-      <c r="X3" s="177"/>
-      <c r="Y3" s="178"/>
+      <c r="W3" s="190"/>
+      <c r="X3" s="190"/>
+      <c r="Y3" s="191"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="191"/>
-      <c r="B4" s="172"/>
+      <c r="A4" s="179"/>
+      <c r="B4" s="185"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -12786,13 +12786,15 @@
       <c r="F129" s="50"/>
       <c r="G129" s="50"/>
       <c r="H129" s="50"/>
-      <c r="I129" s="152"/>
+      <c r="I129" s="152">
+        <v>17987</v>
+      </c>
       <c r="J129" s="50"/>
       <c r="K129" s="50"/>
       <c r="L129" s="50"/>
       <c r="M129" s="152">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>449.67500000000001</v>
       </c>
       <c r="N129" s="39">
         <f t="shared" si="18"/>
@@ -12804,7 +12806,7 @@
       </c>
       <c r="P129" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>899.35</v>
       </c>
       <c r="Q129" s="40">
         <f t="shared" si="98"/>
@@ -12977,10 +12979,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="179" t="s">
+      <c r="B132" s="192" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="180"/>
+      <c r="C132" s="193"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>1320</v>
@@ -13284,10 +13286,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="192" t="s">
+      <c r="B136" s="180" t="s">
         <v>93</v>
       </c>
-      <c r="C136" s="193"/>
+      <c r="C136" s="181"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>1400</v>
@@ -13378,10 +13380,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="181" t="s">
+      <c r="B137" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="182"/>
+      <c r="C137" s="170"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2720</v>
@@ -13432,7 +13434,7 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>3755.1000000000004</v>
+        <v>4654.45</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
@@ -13473,17 +13475,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/june 2026/LMT Orders.xlsx
+++ b/june 2026/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9B76E-D3EB-44BF-B022-080919B18BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABADAAF2-E553-4D1C-9F90-ADC98E7913A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="219">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -1586,7 +1586,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2004,6 +2004,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2043,42 +2082,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2099,6 +2102,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2627,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y137"/>
+  <dimension ref="A1:Y136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -2635,13 +2647,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="182">
+      <c r="B1" s="170">
         <v>46186</v>
       </c>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2663,10 +2675,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="192" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2699,13 +2711,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="171"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="174" t="s">
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="186"/>
+      <c r="P2" s="187" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="175"/>
+      <c r="Q2" s="188"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2724,8 +2736,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="179"/>
-      <c r="B3" s="184"/>
+      <c r="A3" s="192"/>
+      <c r="B3" s="172"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2756,29 +2768,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="176" t="s">
+      <c r="M3" s="189" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="177"/>
-      <c r="O3" s="178"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="191"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="186" t="s">
+      <c r="R3" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="187"/>
-      <c r="T3" s="187"/>
-      <c r="U3" s="188"/>
-      <c r="V3" s="189" t="s">
+      <c r="S3" s="175"/>
+      <c r="T3" s="175"/>
+      <c r="U3" s="176"/>
+      <c r="V3" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="190"/>
-      <c r="X3" s="190"/>
-      <c r="Y3" s="191"/>
+      <c r="W3" s="178"/>
+      <c r="X3" s="178"/>
+      <c r="Y3" s="179"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="179"/>
-      <c r="B4" s="185"/>
+      <c r="A4" s="192"/>
+      <c r="B4" s="173"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2942,7 +2954,7 @@
       <c r="B6" s="47">
         <v>2</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="124" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="74">
@@ -2969,7 +2981,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M137" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M136" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2977,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O136" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O135" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2989,15 +3001,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R136" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R135" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S136" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S135" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T136" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T135" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -3028,7 +3040,7 @@
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="203" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="74">
@@ -3114,7 +3126,7 @@
       <c r="B8" s="47">
         <v>4</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="124" t="s">
         <v>48</v>
       </c>
       <c r="D8" s="74">
@@ -3145,7 +3157,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N136" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N135" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3278,7 +3290,7 @@
       <c r="B10" s="47">
         <v>6</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="204" t="s">
         <v>39</v>
       </c>
       <c r="D10" s="74"/>
@@ -3362,7 +3374,7 @@
       <c r="B11" s="47">
         <v>7</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="124" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="74"/>
@@ -3444,7 +3456,7 @@
       <c r="B12" s="47">
         <v>8</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="202" t="s">
         <v>50</v>
       </c>
       <c r="D12" s="74"/>
@@ -3528,7 +3540,7 @@
       <c r="B13" s="47">
         <v>9</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="204" t="s">
         <v>63</v>
       </c>
       <c r="D13" s="74"/>
@@ -3585,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U136" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U135" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3601,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y136" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y135" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3612,7 +3624,7 @@
       <c r="B14" s="47">
         <v>10</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="204" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="74"/>
@@ -3696,7 +3708,7 @@
       <c r="B15" s="47">
         <v>11</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="204" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="74"/>
@@ -3776,7 +3788,7 @@
       <c r="B16" s="47">
         <v>12</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="202" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="74"/>
@@ -3860,7 +3872,7 @@
       <c r="B17" s="47">
         <v>13</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="204" t="s">
         <v>70</v>
       </c>
       <c r="D17" s="74">
@@ -3940,7 +3952,7 @@
       <c r="B18" s="47">
         <v>14</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="204" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="74"/>
@@ -3965,7 +3977,7 @@
         <v>1199</v>
       </c>
       <c r="M18" s="48">
-        <f t="shared" ref="M18:M20" si="29">SUM(D18:L18)/40</f>
+        <f t="shared" ref="M18:M19" si="29">SUM(D18:L18)/40</f>
         <v>149.35</v>
       </c>
       <c r="N18" s="39">
@@ -3977,11 +3989,11 @@
         <v>331.63</v>
       </c>
       <c r="P18" s="73">
-        <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
+        <f t="shared" ref="P18:P19" si="30">SUM(G18:I18)/20</f>
         <v>99.7</v>
       </c>
       <c r="Q18" s="40">
-        <f t="shared" ref="Q18:Q20" si="31">SUM(J18:L18)/20</f>
+        <f t="shared" ref="Q18:Q19" si="31">SUM(J18:L18)/20</f>
         <v>199</v>
       </c>
       <c r="R18" s="51" t="e">
@@ -3997,23 +4009,23 @@
         <v>0</v>
       </c>
       <c r="U18" s="53" t="e">
-        <f t="shared" ref="U18:U20" si="32">SUM(R18:T18)</f>
+        <f t="shared" ref="U18:U19" si="32">SUM(R18:T18)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V18" s="54" t="e">
-        <f t="shared" ref="V18:V20" si="33">SUM(D18:F18)*$V$3</f>
+        <f t="shared" ref="V18:V19" si="33">SUM(D18:F18)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W18" s="55">
-        <f t="shared" ref="W18:W20" si="34">SUM(G18:I18)*$W$3</f>
+        <f t="shared" ref="W18:W19" si="34">SUM(G18:I18)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X18" s="55">
-        <f t="shared" ref="X18:X20" si="35">SUM(J18:L18)*$X$3</f>
+        <f t="shared" ref="X18:X19" si="35">SUM(J18:L18)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y18" s="56" t="e">
-        <f t="shared" ref="Y18:Y20" si="36">SUM(V18:X18)</f>
+        <f t="shared" ref="Y18:Y19" si="36">SUM(V18:X18)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4024,7 +4036,7 @@
       <c r="B19" s="47">
         <v>15</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="124" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="74"/>
@@ -4099,38 +4111,38 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" s="78">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B20" s="47">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D20" s="74"/>
       <c r="E20" s="75"/>
       <c r="F20" s="76"/>
       <c r="G20" s="50">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="H20" s="75">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="I20" s="49">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="J20" s="50">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="K20" s="75">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="L20" s="76">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="M20" s="48">
-        <f t="shared" si="29"/>
-        <v>6</v>
+        <f t="shared" ref="M20:M22" si="37">SUM(D20:L20)/40</f>
+        <v>18</v>
       </c>
       <c r="N20" s="39">
         <f t="shared" si="18"/>
@@ -4141,12 +4153,12 @@
         <v>331.63</v>
       </c>
       <c r="P20" s="73">
-        <f t="shared" si="30"/>
-        <v>6</v>
+        <f t="shared" ref="P20:P22" si="38">SUM(G20:I20)/20</f>
+        <v>18</v>
       </c>
       <c r="Q20" s="40">
-        <f t="shared" si="31"/>
-        <v>6</v>
+        <f t="shared" ref="Q20:Q22" si="39">SUM(J20:L20)/20</f>
+        <v>18</v>
       </c>
       <c r="R20" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4161,23 +4173,23 @@
         <v>0</v>
       </c>
       <c r="U20" s="53" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="U20:U21" si="40">SUM(R20:T20)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V20" s="54" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="V20:V21" si="41">SUM(D20:F20)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W20" s="55">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="W20:W22" si="42">SUM(G20:I20)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X20" s="55">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="X20:X22" si="43">SUM(J20:L20)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y20" s="56" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="Y20:Y131" si="44">SUM(V20:X20)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4185,36 +4197,36 @@
       <c r="A21" s="78">
         <v>46185</v>
       </c>
-      <c r="B21" s="47">
-        <v>17</v>
-      </c>
-      <c r="C21" s="57" t="s">
+      <c r="B21" s="130">
+        <v>18</v>
+      </c>
+      <c r="C21" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="50">
-        <v>120</v>
-      </c>
-      <c r="H21" s="75">
-        <v>120</v>
-      </c>
-      <c r="I21" s="49">
-        <v>120</v>
-      </c>
-      <c r="J21" s="50">
-        <v>120</v>
-      </c>
-      <c r="K21" s="75">
-        <v>120</v>
-      </c>
-      <c r="L21" s="76">
-        <v>120</v>
-      </c>
-      <c r="M21" s="48">
-        <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
-        <v>18</v>
+      <c r="D21" s="131"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="128">
+        <v>300</v>
+      </c>
+      <c r="H21" s="126">
+        <v>300</v>
+      </c>
+      <c r="I21" s="56">
+        <v>300</v>
+      </c>
+      <c r="J21" s="128">
+        <v>300</v>
+      </c>
+      <c r="K21" s="126">
+        <v>300</v>
+      </c>
+      <c r="L21" s="127">
+        <v>300</v>
+      </c>
+      <c r="M21" s="129">
+        <f t="shared" si="37"/>
+        <v>45</v>
       </c>
       <c r="N21" s="39">
         <f t="shared" si="18"/>
@@ -4225,12 +4237,12 @@
         <v>331.63</v>
       </c>
       <c r="P21" s="73">
-        <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
-        <v>18</v>
+        <f t="shared" si="38"/>
+        <v>45</v>
       </c>
       <c r="Q21" s="40">
-        <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
-        <v>18</v>
+        <f t="shared" si="39"/>
+        <v>45</v>
       </c>
       <c r="R21" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4245,60 +4257,60 @@
         <v>0</v>
       </c>
       <c r="U21" s="53" t="e">
-        <f t="shared" ref="U21:U22" si="40">SUM(R21:T21)</f>
+        <f t="shared" si="40"/>
         <v>#VALUE!</v>
       </c>
       <c r="V21" s="54" t="e">
-        <f t="shared" ref="V21:V22" si="41">SUM(D21:F21)*$V$3</f>
+        <f t="shared" si="41"/>
         <v>#VALUE!</v>
       </c>
       <c r="W21" s="55">
-        <f t="shared" ref="W21:W23" si="42">SUM(G21:I21)*$W$3</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="X21" s="55">
-        <f t="shared" ref="X21:X23" si="43">SUM(J21:L21)*$X$3</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y132" si="44">SUM(V21:X21)</f>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="78">
-        <v>46185</v>
-      </c>
-      <c r="B22" s="130">
-        <v>18</v>
-      </c>
-      <c r="C22" s="124" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="131"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="128">
-        <v>300</v>
-      </c>
-      <c r="H22" s="126">
-        <v>300</v>
-      </c>
-      <c r="I22" s="56">
-        <v>300</v>
-      </c>
-      <c r="J22" s="128">
-        <v>300</v>
-      </c>
-      <c r="K22" s="126">
-        <v>300</v>
-      </c>
-      <c r="L22" s="127">
-        <v>300</v>
-      </c>
-      <c r="M22" s="129">
+        <v>46189</v>
+      </c>
+      <c r="B22" s="47">
+        <v>19</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="74"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="134">
+        <v>80</v>
+      </c>
+      <c r="H22" s="135">
+        <v>80</v>
+      </c>
+      <c r="I22" s="136">
+        <v>80</v>
+      </c>
+      <c r="J22" s="134">
+        <v>80</v>
+      </c>
+      <c r="K22" s="135">
+        <v>80</v>
+      </c>
+      <c r="L22" s="137">
+        <v>80</v>
+      </c>
+      <c r="M22" s="48">
         <f t="shared" si="37"/>
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="N22" s="39">
         <f t="shared" si="18"/>
@@ -4310,11 +4322,11 @@
       </c>
       <c r="P22" s="73">
         <f t="shared" si="38"/>
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="39"/>
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="R22" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4329,11 +4341,11 @@
         <v>0</v>
       </c>
       <c r="U22" s="53" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="U22:U26" si="45">SUM(R22:T22)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V22" s="54" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="V22:V26" si="46">SUM(D22:F22)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W22" s="55">
@@ -4354,10 +4366,10 @@
         <v>46189</v>
       </c>
       <c r="B23" s="47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
@@ -4381,7 +4393,7 @@
         <v>80</v>
       </c>
       <c r="M23" s="48">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="M23:M26" si="47">SUM(D23:L23)/40</f>
         <v>12</v>
       </c>
       <c r="N23" s="39">
@@ -4393,11 +4405,11 @@
         <v>331.63</v>
       </c>
       <c r="P23" s="73">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="P23:P26" si="48">SUM(G23:I23)/20</f>
         <v>12</v>
       </c>
       <c r="Q23" s="40">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="Q23:Q26" si="49">SUM(J23:L23)/20</f>
         <v>12</v>
       </c>
       <c r="R23" s="51" t="e">
@@ -4413,19 +4425,19 @@
         <v>0</v>
       </c>
       <c r="U23" s="53" t="e">
-        <f t="shared" ref="U23:U27" si="45">SUM(R23:T23)</f>
+        <f t="shared" si="45"/>
         <v>#VALUE!</v>
       </c>
       <c r="V23" s="54" t="e">
-        <f t="shared" ref="V23:V27" si="46">SUM(D23:F23)*$V$3</f>
+        <f t="shared" si="46"/>
         <v>#VALUE!</v>
       </c>
       <c r="W23" s="55">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="W23:W26" si="50">SUM(G23:I23)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X23" s="55">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="X23:X26" si="51">SUM(J23:L23)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y23" s="56" t="e">
@@ -4438,10 +4450,10 @@
         <v>46189</v>
       </c>
       <c r="B24" s="47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
@@ -4465,7 +4477,7 @@
         <v>80</v>
       </c>
       <c r="M24" s="48">
-        <f t="shared" ref="M24:M27" si="47">SUM(D24:L24)/40</f>
+        <f t="shared" si="47"/>
         <v>12</v>
       </c>
       <c r="N24" s="39">
@@ -4477,11 +4489,11 @@
         <v>331.63</v>
       </c>
       <c r="P24" s="73">
-        <f t="shared" ref="P24:P27" si="48">SUM(G24:I24)/20</f>
+        <f t="shared" si="48"/>
         <v>12</v>
       </c>
       <c r="Q24" s="40">
-        <f t="shared" ref="Q24:Q27" si="49">SUM(J24:L24)/20</f>
+        <f t="shared" si="49"/>
         <v>12</v>
       </c>
       <c r="R24" s="51" t="e">
@@ -4505,11 +4517,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="W24" s="55">
-        <f t="shared" ref="W24:W27" si="50">SUM(G24:I24)*$W$3</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="X24" s="55">
-        <f t="shared" ref="X24:X27" si="51">SUM(J24:L24)*$X$3</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="Y24" s="56" t="e">
@@ -4522,35 +4534,35 @@
         <v>46189</v>
       </c>
       <c r="B25" s="47">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D25" s="74"/>
       <c r="E25" s="75"/>
       <c r="F25" s="76"/>
       <c r="G25" s="134">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H25" s="135">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I25" s="136">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J25" s="134">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K25" s="135">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L25" s="137">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M25" s="48">
         <f t="shared" si="47"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N25" s="39">
         <f t="shared" si="18"/>
@@ -4562,11 +4574,11 @@
       </c>
       <c r="P25" s="73">
         <f t="shared" si="48"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="49"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R25" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4606,35 +4618,37 @@
         <v>46189</v>
       </c>
       <c r="B26" s="47">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="74"/>
+        <v>88</v>
+      </c>
+      <c r="D26" s="74">
+        <v>80</v>
+      </c>
       <c r="E26" s="75"/>
       <c r="F26" s="76"/>
       <c r="G26" s="134">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H26" s="135">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I26" s="136">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J26" s="134">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K26" s="135">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L26" s="137">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M26" s="48">
         <f t="shared" si="47"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N26" s="39">
         <f t="shared" si="18"/>
@@ -4646,11 +4660,11 @@
       </c>
       <c r="P26" s="73">
         <f t="shared" si="48"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="49"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R26" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4690,37 +4704,37 @@
         <v>46189</v>
       </c>
       <c r="B27" s="47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="74">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E27" s="75"/>
       <c r="F27" s="76"/>
       <c r="G27" s="134">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H27" s="135">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I27" s="136">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J27" s="134">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K27" s="135">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="L27" s="137">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="M27" s="48">
-        <f t="shared" si="47"/>
-        <v>14</v>
+        <f t="shared" ref="M27:M59" si="52">SUM(D27:L27)/40</f>
+        <v>21</v>
       </c>
       <c r="N27" s="39">
         <f t="shared" si="18"/>
@@ -4731,12 +4745,12 @@
         <v>331.63</v>
       </c>
       <c r="P27" s="73">
-        <f t="shared" si="48"/>
-        <v>12</v>
+        <f t="shared" ref="P27:P59" si="53">SUM(G27:I27)/20</f>
+        <v>18</v>
       </c>
       <c r="Q27" s="40">
-        <f t="shared" si="49"/>
-        <v>12</v>
+        <f t="shared" ref="Q27:Q59" si="54">SUM(J27:L27)/20</f>
+        <v>18</v>
       </c>
       <c r="R27" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4751,23 +4765,23 @@
         <v>0</v>
       </c>
       <c r="U27" s="53" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="U27:U59" si="55">SUM(R27:T27)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V27" s="54" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="V27:V59" si="56">SUM(D27:F27)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W27" s="55">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="W27:W59" si="57">SUM(G27:I27)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X27" s="55">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="X27:X59" si="58">SUM(J27:L27)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y27" s="56" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="Y27:Y59" si="59">SUM(V27:X27)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4776,37 +4790,33 @@
         <v>46189</v>
       </c>
       <c r="B28" s="47">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="74">
-        <v>120</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="D28" s="74"/>
       <c r="E28" s="75"/>
       <c r="F28" s="76"/>
       <c r="G28" s="134">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="H28" s="135">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I28" s="136">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J28" s="134">
-        <v>120</v>
-      </c>
-      <c r="K28" s="135">
-        <v>120</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K28" s="135"/>
       <c r="L28" s="137">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="M28" s="48">
-        <f t="shared" ref="M28:M60" si="52">SUM(D28:L28)/40</f>
-        <v>21</v>
+        <f t="shared" ref="M28" si="60">SUM(D28:L28)/40</f>
+        <v>7</v>
       </c>
       <c r="N28" s="39">
         <f t="shared" si="18"/>
@@ -4817,12 +4827,12 @@
         <v>331.63</v>
       </c>
       <c r="P28" s="73">
-        <f t="shared" ref="P28:P60" si="53">SUM(G28:I28)/20</f>
-        <v>18</v>
+        <f t="shared" ref="P28" si="61">SUM(G28:I28)/20</f>
+        <v>8</v>
       </c>
       <c r="Q28" s="40">
-        <f t="shared" ref="Q28:Q60" si="54">SUM(J28:L28)/20</f>
-        <v>18</v>
+        <f t="shared" ref="Q28" si="62">SUM(J28:L28)/20</f>
+        <v>6</v>
       </c>
       <c r="R28" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4837,58 +4847,60 @@
         <v>0</v>
       </c>
       <c r="U28" s="53" t="e">
-        <f t="shared" ref="U28:U60" si="55">SUM(R28:T28)</f>
+        <f t="shared" ref="U28" si="63">SUM(R28:T28)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V28" s="54" t="e">
-        <f t="shared" ref="V28:V60" si="56">SUM(D28:F28)*$V$3</f>
+        <f t="shared" ref="V28" si="64">SUM(D28:F28)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W28" s="55">
-        <f t="shared" ref="W28:W60" si="57">SUM(G28:I28)*$W$3</f>
+        <f t="shared" ref="W28" si="65">SUM(G28:I28)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X28" s="55">
-        <f t="shared" ref="X28:X60" si="58">SUM(J28:L28)*$X$3</f>
+        <f t="shared" ref="X28" si="66">SUM(J28:L28)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y28" s="56" t="e">
-        <f t="shared" ref="Y28:Y60" si="59">SUM(V28:X28)</f>
+        <f t="shared" ref="Y28" si="67">SUM(V28:X28)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" s="78">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B29" s="47">
-        <v>25</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>107</v>
+        <v>26</v>
+      </c>
+      <c r="C29" s="203" t="s">
+        <v>44</v>
       </c>
       <c r="D29" s="74"/>
       <c r="E29" s="75"/>
       <c r="F29" s="76"/>
-      <c r="G29" s="134">
-        <v>40</v>
-      </c>
-      <c r="H29" s="135">
-        <v>40</v>
-      </c>
-      <c r="I29" s="136">
-        <v>80</v>
-      </c>
-      <c r="J29" s="134">
-        <v>40</v>
-      </c>
-      <c r="K29" s="135"/>
-      <c r="L29" s="137">
-        <v>80</v>
+      <c r="G29" s="50">
+        <v>80</v>
+      </c>
+      <c r="H29" s="75">
+        <v>80</v>
+      </c>
+      <c r="I29" s="49">
+        <v>200</v>
+      </c>
+      <c r="J29" s="50">
+        <v>80</v>
+      </c>
+      <c r="K29" s="75">
+        <v>80</v>
+      </c>
+      <c r="L29" s="76">
+        <v>200</v>
       </c>
       <c r="M29" s="48">
-        <f t="shared" ref="M29" si="60">SUM(D29:L29)/40</f>
-        <v>7</v>
+        <f t="shared" si="52"/>
+        <v>18</v>
       </c>
       <c r="N29" s="39">
         <f t="shared" si="18"/>
@@ -4899,12 +4911,12 @@
         <v>331.63</v>
       </c>
       <c r="P29" s="73">
-        <f t="shared" ref="P29" si="61">SUM(G29:I29)/20</f>
-        <v>8</v>
+        <f t="shared" si="53"/>
+        <v>18</v>
       </c>
       <c r="Q29" s="40">
-        <f t="shared" ref="Q29" si="62">SUM(J29:L29)/20</f>
-        <v>6</v>
+        <f t="shared" si="54"/>
+        <v>18</v>
       </c>
       <c r="R29" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4919,23 +4931,23 @@
         <v>0</v>
       </c>
       <c r="U29" s="53" t="e">
-        <f t="shared" ref="U29" si="63">SUM(R29:T29)</f>
+        <f t="shared" si="55"/>
         <v>#VALUE!</v>
       </c>
       <c r="V29" s="54" t="e">
-        <f t="shared" ref="V29" si="64">SUM(D29:F29)*$V$3</f>
+        <f t="shared" si="56"/>
         <v>#VALUE!</v>
       </c>
       <c r="W29" s="55">
-        <f t="shared" ref="W29" si="65">SUM(G29:I29)*$W$3</f>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="X29" s="55">
-        <f t="shared" ref="X29" si="66">SUM(J29:L29)*$X$3</f>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Y29" s="56" t="e">
-        <f t="shared" ref="Y29" si="67">SUM(V29:X29)</f>
+        <f t="shared" si="59"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4944,10 +4956,10 @@
         <v>46190</v>
       </c>
       <c r="B30" s="47">
-        <v>26</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>44</v>
+        <v>27</v>
+      </c>
+      <c r="C30" s="204" t="s">
+        <v>90</v>
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="75"/>
@@ -4959,7 +4971,7 @@
         <v>80</v>
       </c>
       <c r="I30" s="49">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="J30" s="50">
         <v>80</v>
@@ -4968,11 +4980,11 @@
         <v>80</v>
       </c>
       <c r="L30" s="76">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="M30" s="48">
         <f t="shared" si="52"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N30" s="39">
         <f t="shared" si="18"/>
@@ -4984,11 +4996,11 @@
       </c>
       <c r="P30" s="73">
         <f t="shared" si="53"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="54"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R30" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5028,35 +5040,35 @@
         <v>46190</v>
       </c>
       <c r="B31" s="47">
-        <v>27</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="50">
-        <v>80</v>
-      </c>
-      <c r="H31" s="75">
-        <v>80</v>
-      </c>
-      <c r="I31" s="49">
-        <v>80</v>
-      </c>
-      <c r="J31" s="50">
-        <v>80</v>
-      </c>
-      <c r="K31" s="75">
-        <v>80</v>
-      </c>
-      <c r="L31" s="76">
-        <v>80</v>
-      </c>
-      <c r="M31" s="48">
+        <v>28</v>
+      </c>
+      <c r="C31" s="202" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="125"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="127"/>
+      <c r="G31" s="128">
+        <v>40</v>
+      </c>
+      <c r="H31" s="126">
+        <v>40</v>
+      </c>
+      <c r="I31" s="56">
+        <v>80</v>
+      </c>
+      <c r="J31" s="128">
+        <v>80</v>
+      </c>
+      <c r="K31" s="126">
+        <v>120</v>
+      </c>
+      <c r="L31" s="127">
+        <v>40</v>
+      </c>
+      <c r="M31" s="129">
         <f t="shared" si="52"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N31" s="39">
         <f t="shared" si="18"/>
@@ -5068,7 +5080,7 @@
       </c>
       <c r="P31" s="73">
         <f t="shared" si="53"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="54"/>
@@ -5112,35 +5124,37 @@
         <v>46190</v>
       </c>
       <c r="B32" s="47">
-        <v>28</v>
-      </c>
-      <c r="C32" s="124" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="125"/>
-      <c r="E32" s="126"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="128">
-        <v>40</v>
-      </c>
-      <c r="H32" s="126">
-        <v>40</v>
-      </c>
-      <c r="I32" s="56">
-        <v>80</v>
-      </c>
-      <c r="J32" s="128">
-        <v>80</v>
-      </c>
-      <c r="K32" s="126">
-        <v>120</v>
-      </c>
-      <c r="L32" s="127">
-        <v>40</v>
-      </c>
-      <c r="M32" s="129">
+        <v>29</v>
+      </c>
+      <c r="C32" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="74"/>
+      <c r="E32" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="76"/>
+      <c r="G32" s="50">
+        <v>40</v>
+      </c>
+      <c r="H32" s="75">
+        <v>40</v>
+      </c>
+      <c r="I32" s="49">
+        <v>40</v>
+      </c>
+      <c r="J32" s="50">
+        <v>40</v>
+      </c>
+      <c r="K32" s="75">
+        <v>40</v>
+      </c>
+      <c r="L32" s="76">
+        <v>40</v>
+      </c>
+      <c r="M32" s="48">
         <f t="shared" si="52"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N32" s="39">
         <f t="shared" si="18"/>
@@ -5152,11 +5166,11 @@
       </c>
       <c r="P32" s="73">
         <f t="shared" si="53"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="54"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R32" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5196,15 +5210,13 @@
         <v>46190</v>
       </c>
       <c r="B33" s="47">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D33" s="74"/>
-      <c r="E33" s="75" t="s">
-        <v>92</v>
-      </c>
+      <c r="E33" s="75"/>
       <c r="F33" s="76"/>
       <c r="G33" s="50">
         <v>40</v>
@@ -5225,7 +5237,7 @@
         <v>40</v>
       </c>
       <c r="M33" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="M33:M45" si="68">SUM(D33:L33)/40</f>
         <v>6</v>
       </c>
       <c r="N33" s="39">
@@ -5237,11 +5249,11 @@
         <v>331.63</v>
       </c>
       <c r="P33" s="73">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="P33:P45" si="69">SUM(G33:I33)/20</f>
         <v>6</v>
       </c>
       <c r="Q33" s="40">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="Q33:Q45" si="70">SUM(J33:L33)/20</f>
         <v>6</v>
       </c>
       <c r="R33" s="51" t="e">
@@ -5257,23 +5269,23 @@
         <v>0</v>
       </c>
       <c r="U33" s="53" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="U33:U44" si="71">SUM(R33:T33)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V33" s="54" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="V33:V44" si="72">SUM(D33:F33)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W33" s="55">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="W33:W45" si="73">SUM(G33:I33)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X33" s="55">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="X33:X45" si="74">SUM(J33:L33)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y33" s="56" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="Y33:Y44" si="75">SUM(V33:X33)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -5282,10 +5294,10 @@
         <v>46190</v>
       </c>
       <c r="B34" s="47">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D34" s="74"/>
       <c r="E34" s="75"/>
@@ -5309,7 +5321,7 @@
         <v>40</v>
       </c>
       <c r="M34" s="48">
-        <f t="shared" ref="M34:M46" si="68">SUM(D34:L34)/40</f>
+        <f t="shared" si="68"/>
         <v>6</v>
       </c>
       <c r="N34" s="39">
@@ -5321,11 +5333,11 @@
         <v>331.63</v>
       </c>
       <c r="P34" s="73">
-        <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
+        <f t="shared" si="69"/>
         <v>6</v>
       </c>
       <c r="Q34" s="40">
-        <f t="shared" ref="Q34:Q46" si="70">SUM(J34:L34)/20</f>
+        <f t="shared" si="70"/>
         <v>6</v>
       </c>
       <c r="R34" s="51" t="e">
@@ -5341,23 +5353,23 @@
         <v>0</v>
       </c>
       <c r="U34" s="53" t="e">
-        <f t="shared" ref="U34:U45" si="71">SUM(R34:T34)</f>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="V34" s="54" t="e">
-        <f t="shared" ref="V34:V45" si="72">SUM(D34:F34)*$V$3</f>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="W34" s="55">
-        <f t="shared" ref="W34:W46" si="73">SUM(G34:I34)*$W$3</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="X34" s="55">
-        <f t="shared" ref="X34:X46" si="74">SUM(J34:L34)*$X$3</f>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="Y34" s="56" t="e">
-        <f t="shared" ref="Y34:Y45" si="75">SUM(V34:X34)</f>
+        <f t="shared" si="75"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -5366,10 +5378,10 @@
         <v>46190</v>
       </c>
       <c r="B35" s="47">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
@@ -5450,35 +5462,35 @@
         <v>46190</v>
       </c>
       <c r="B36" s="47">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D36" s="74"/>
       <c r="E36" s="75"/>
       <c r="F36" s="76"/>
       <c r="G36" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H36" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I36" s="49">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J36" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K36" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L36" s="76">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M36" s="48">
         <f t="shared" si="68"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N36" s="39">
         <f t="shared" si="18"/>
@@ -5490,11 +5502,11 @@
       </c>
       <c r="P36" s="73">
         <f t="shared" si="69"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="70"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R36" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5534,35 +5546,35 @@
         <v>46190</v>
       </c>
       <c r="B37" s="47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" s="74"/>
       <c r="E37" s="75"/>
       <c r="F37" s="76"/>
       <c r="G37" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H37" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I37" s="49">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J37" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K37" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L37" s="76">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M37" s="48">
         <f t="shared" si="68"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N37" s="39">
         <f t="shared" si="18"/>
@@ -5574,11 +5586,11 @@
       </c>
       <c r="P37" s="73">
         <f t="shared" si="69"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" si="70"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R37" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5618,35 +5630,35 @@
         <v>46190</v>
       </c>
       <c r="B38" s="47">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38" s="74"/>
       <c r="E38" s="75"/>
       <c r="F38" s="76"/>
       <c r="G38" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H38" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I38" s="49">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J38" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K38" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L38" s="76">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M38" s="48">
         <f t="shared" si="68"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N38" s="39">
         <f t="shared" si="18"/>
@@ -5658,11 +5670,11 @@
       </c>
       <c r="P38" s="73">
         <f t="shared" si="69"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q38" s="40">
         <f t="shared" si="70"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R38" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5702,10 +5714,10 @@
         <v>46190</v>
       </c>
       <c r="B39" s="47">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D39" s="74"/>
       <c r="E39" s="75"/>
@@ -5786,35 +5798,35 @@
         <v>46190</v>
       </c>
       <c r="B40" s="47">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D40" s="74"/>
       <c r="E40" s="75"/>
       <c r="F40" s="76"/>
       <c r="G40" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H40" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I40" s="49">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J40" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K40" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L40" s="76">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M40" s="48">
         <f t="shared" si="68"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N40" s="39">
         <f t="shared" si="18"/>
@@ -5826,11 +5838,11 @@
       </c>
       <c r="P40" s="73">
         <f t="shared" si="69"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q40" s="40">
         <f t="shared" si="70"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R40" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5870,10 +5882,10 @@
         <v>46190</v>
       </c>
       <c r="B41" s="47">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D41" s="74"/>
       <c r="E41" s="75"/>
@@ -5954,10 +5966,10 @@
         <v>46190</v>
       </c>
       <c r="B42" s="47">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D42" s="74"/>
       <c r="E42" s="75"/>
@@ -6038,35 +6050,35 @@
         <v>46190</v>
       </c>
       <c r="B43" s="47">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D43" s="74"/>
       <c r="E43" s="75"/>
       <c r="F43" s="76"/>
       <c r="G43" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H43" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I43" s="49">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J43" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K43" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L43" s="76">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M43" s="48">
         <f t="shared" si="68"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N43" s="39">
         <f t="shared" si="18"/>
@@ -6078,11 +6090,11 @@
       </c>
       <c r="P43" s="73">
         <f t="shared" si="69"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q43" s="40">
         <f t="shared" si="70"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R43" s="51" t="e">
         <f t="shared" si="4"/>
@@ -6119,38 +6131,38 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" s="78">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B44" s="47">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D44" s="74"/>
       <c r="E44" s="75"/>
       <c r="F44" s="76"/>
       <c r="G44" s="50">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H44" s="75">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="I44" s="49">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="J44" s="50">
-        <v>80</v>
+        <v>520</v>
       </c>
       <c r="K44" s="75">
-        <v>80</v>
+        <v>760</v>
       </c>
       <c r="L44" s="76">
-        <v>80</v>
+        <v>760</v>
       </c>
       <c r="M44" s="48">
         <f t="shared" si="68"/>
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="N44" s="39">
         <f t="shared" si="18"/>
@@ -6162,11 +6174,11 @@
       </c>
       <c r="P44" s="73">
         <f t="shared" si="69"/>
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="Q44" s="40">
         <f t="shared" si="70"/>
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="R44" s="51" t="e">
         <f t="shared" si="4"/>
@@ -6206,35 +6218,35 @@
         <v>46191</v>
       </c>
       <c r="B45" s="47">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D45" s="74"/>
       <c r="E45" s="75"/>
       <c r="F45" s="76"/>
       <c r="G45" s="50">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="H45" s="75">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="I45" s="49">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="J45" s="50">
-        <v>520</v>
+        <v>40</v>
       </c>
       <c r="K45" s="75">
-        <v>760</v>
+        <v>40</v>
       </c>
       <c r="L45" s="76">
-        <v>760</v>
+        <v>40</v>
       </c>
       <c r="M45" s="48">
         <f t="shared" si="68"/>
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="N45" s="39">
         <f t="shared" si="18"/>
@@ -6246,32 +6258,17 @@
       </c>
       <c r="P45" s="73">
         <f t="shared" si="69"/>
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="40">
         <f t="shared" si="70"/>
-        <v>102</v>
-      </c>
-      <c r="R45" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S45" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T45" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U45" s="53" t="e">
-        <f t="shared" si="71"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V45" s="54" t="e">
-        <f t="shared" si="72"/>
-        <v>#VALUE!</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="R45" s="51"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="53"/>
+      <c r="V45" s="54"/>
       <c r="W45" s="55">
         <f t="shared" si="73"/>
         <v>0</v>
@@ -6280,20 +6277,17 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="Y45" s="56" t="e">
-        <f t="shared" si="75"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="Y45" s="56"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" s="78">
         <v>46191</v>
       </c>
       <c r="B46" s="47">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D46" s="74"/>
       <c r="E46" s="75"/>
@@ -6317,7 +6311,7 @@
         <v>40</v>
       </c>
       <c r="M46" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" ref="M46:M58" si="76">SUM(D46:L46)/40</f>
         <v>6</v>
       </c>
       <c r="N46" s="39">
@@ -6329,11 +6323,11 @@
         <v>331.63</v>
       </c>
       <c r="P46" s="73">
-        <f t="shared" si="69"/>
+        <f t="shared" ref="P46:P58" si="77">SUM(G46:I46)/20</f>
         <v>6</v>
       </c>
       <c r="Q46" s="40">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="Q46:Q58" si="78">SUM(J46:L46)/20</f>
         <v>6</v>
       </c>
       <c r="R46" s="51"/>
@@ -6342,11 +6336,11 @@
       <c r="U46" s="53"/>
       <c r="V46" s="54"/>
       <c r="W46" s="55">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="W46:W58" si="79">SUM(G46:I46)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X46" s="55">
-        <f t="shared" si="74"/>
+        <f t="shared" ref="X46:X58" si="80">SUM(J46:L46)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y46" s="56"/>
@@ -6356,10 +6350,10 @@
         <v>46191</v>
       </c>
       <c r="B47" s="47">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D47" s="74"/>
       <c r="E47" s="75"/>
@@ -6383,7 +6377,7 @@
         <v>40</v>
       </c>
       <c r="M47" s="48">
-        <f t="shared" ref="M47:M59" si="76">SUM(D47:L47)/40</f>
+        <f t="shared" si="76"/>
         <v>6</v>
       </c>
       <c r="N47" s="39">
@@ -6395,11 +6389,11 @@
         <v>331.63</v>
       </c>
       <c r="P47" s="73">
-        <f t="shared" ref="P47:P59" si="77">SUM(G47:I47)/20</f>
+        <f t="shared" si="77"/>
         <v>6</v>
       </c>
       <c r="Q47" s="40">
-        <f t="shared" ref="Q47:Q59" si="78">SUM(J47:L47)/20</f>
+        <f t="shared" si="78"/>
         <v>6</v>
       </c>
       <c r="R47" s="51"/>
@@ -6408,11 +6402,11 @@
       <c r="U47" s="53"/>
       <c r="V47" s="54"/>
       <c r="W47" s="55">
-        <f t="shared" ref="W47:W59" si="79">SUM(G47:I47)*$W$3</f>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="X47" s="55">
-        <f t="shared" ref="X47:X59" si="80">SUM(J47:L47)*$X$3</f>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="Y47" s="56"/>
@@ -6422,10 +6416,10 @@
         <v>46191</v>
       </c>
       <c r="B48" s="47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D48" s="74"/>
       <c r="E48" s="75"/>
@@ -6488,10 +6482,10 @@
         <v>46191</v>
       </c>
       <c r="B49" s="47">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D49" s="74"/>
       <c r="E49" s="75"/>
@@ -6554,10 +6548,10 @@
         <v>46191</v>
       </c>
       <c r="B50" s="47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C50" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D50" s="74"/>
       <c r="E50" s="75"/>
@@ -6620,10 +6614,10 @@
         <v>46191</v>
       </c>
       <c r="B51" s="47">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D51" s="74"/>
       <c r="E51" s="75"/>
@@ -6686,10 +6680,10 @@
         <v>46191</v>
       </c>
       <c r="B52" s="47">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C52" s="57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D52" s="74"/>
       <c r="E52" s="75"/>
@@ -6752,10 +6746,10 @@
         <v>46191</v>
       </c>
       <c r="B53" s="47">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D53" s="74"/>
       <c r="E53" s="75"/>
@@ -6818,10 +6812,10 @@
         <v>46191</v>
       </c>
       <c r="B54" s="47">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D54" s="74"/>
       <c r="E54" s="75"/>
@@ -6884,10 +6878,10 @@
         <v>46191</v>
       </c>
       <c r="B55" s="47">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C55" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D55" s="74"/>
       <c r="E55" s="75"/>
@@ -6950,33 +6944,33 @@
         <v>46191</v>
       </c>
       <c r="B56" s="47">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" s="74"/>
+        <v>125</v>
+      </c>
+      <c r="D56" s="75"/>
       <c r="E56" s="75"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="50">
+      <c r="F56" s="75"/>
+      <c r="G56" s="75">
         <v>40</v>
       </c>
       <c r="H56" s="75">
         <v>40</v>
       </c>
-      <c r="I56" s="49">
-        <v>40</v>
-      </c>
-      <c r="J56" s="50">
+      <c r="I56" s="153">
+        <v>40</v>
+      </c>
+      <c r="J56" s="75">
         <v>40</v>
       </c>
       <c r="K56" s="75">
         <v>40</v>
       </c>
-      <c r="L56" s="76">
-        <v>40</v>
-      </c>
-      <c r="M56" s="48">
+      <c r="L56" s="75">
+        <v>40</v>
+      </c>
+      <c r="M56" s="152">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -7016,10 +7010,10 @@
         <v>46191</v>
       </c>
       <c r="B57" s="47">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D57" s="75"/>
       <c r="E57" s="75"/>
@@ -7082,10 +7076,10 @@
         <v>46191</v>
       </c>
       <c r="B58" s="47">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C58" s="57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D58" s="75"/>
       <c r="E58" s="75"/>
@@ -7148,35 +7142,35 @@
         <v>46191</v>
       </c>
       <c r="B59" s="47">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C59" s="57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D59" s="75"/>
       <c r="E59" s="75"/>
       <c r="F59" s="75"/>
       <c r="G59" s="75">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="H59" s="75">
-        <v>40</v>
+        <v>1200</v>
       </c>
       <c r="I59" s="153">
-        <v>40</v>
+        <v>2800</v>
       </c>
       <c r="J59" s="75">
-        <v>40</v>
+        <v>1800</v>
       </c>
       <c r="K59" s="75">
-        <v>40</v>
+        <v>1200</v>
       </c>
       <c r="L59" s="75">
-        <v>40</v>
+        <v>3600</v>
       </c>
       <c r="M59" s="152">
-        <f t="shared" si="76"/>
-        <v>6</v>
+        <f t="shared" si="52"/>
+        <v>285</v>
       </c>
       <c r="N59" s="39">
         <f t="shared" si="18"/>
@@ -7187,62 +7181,80 @@
         <v>331.63</v>
       </c>
       <c r="P59" s="73">
-        <f t="shared" si="77"/>
-        <v>6</v>
+        <f t="shared" si="53"/>
+        <v>240</v>
       </c>
       <c r="Q59" s="40">
-        <f t="shared" si="78"/>
-        <v>6</v>
-      </c>
-      <c r="R59" s="51"/>
-      <c r="S59" s="52"/>
-      <c r="T59" s="52"/>
-      <c r="U59" s="53"/>
-      <c r="V59" s="54"/>
+        <f t="shared" si="54"/>
+        <v>330</v>
+      </c>
+      <c r="R59" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S59" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U59" s="53" t="e">
+        <f t="shared" si="55"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V59" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="W59" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="X59" s="55">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="Y59" s="56"/>
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="56" t="e">
+        <f t="shared" si="59"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="78">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B60" s="47">
-        <v>56</v>
-      </c>
-      <c r="C60" s="57" t="s">
-        <v>128</v>
+        <v>57</v>
+      </c>
+      <c r="C60" s="151" t="s">
+        <v>139</v>
       </c>
       <c r="D60" s="75"/>
       <c r="E60" s="75"/>
       <c r="F60" s="75"/>
       <c r="G60" s="75">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="H60" s="75">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I60" s="153">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="J60" s="75">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="K60" s="75">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L60" s="75">
-        <v>3600</v>
+        <v>400</v>
       </c>
       <c r="M60" s="152">
-        <f t="shared" si="52"/>
-        <v>285</v>
+        <f t="shared" ref="M60:M82" si="81">SUM(D60:L60)/40</f>
+        <v>22</v>
       </c>
       <c r="N60" s="39">
         <f t="shared" si="18"/>
@@ -7253,12 +7265,12 @@
         <v>331.63</v>
       </c>
       <c r="P60" s="73">
-        <f t="shared" si="53"/>
-        <v>240</v>
+        <f t="shared" ref="P60:P77" si="82">SUM(G60:I60)/20</f>
+        <v>14</v>
       </c>
       <c r="Q60" s="40">
-        <f t="shared" si="54"/>
-        <v>330</v>
+        <f t="shared" ref="Q60:Q77" si="83">SUM(J60:L60)/20</f>
+        <v>30</v>
       </c>
       <c r="R60" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7273,23 +7285,23 @@
         <v>0</v>
       </c>
       <c r="U60" s="53" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="U60:U77" si="84">SUM(R60:T60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V60" s="54" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="V60:V77" si="85">SUM(D60:F60)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W60" s="55">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="W60:W77" si="86">SUM(G60:I60)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X60" s="55">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="X60:X77" si="87">SUM(J60:L60)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y60" s="56" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="Y60:Y77" si="88">SUM(V60:X60)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7298,10 +7310,10 @@
         <v>46192</v>
       </c>
       <c r="B61" s="47">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C61" s="151" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
@@ -7310,23 +7322,23 @@
         <v>80</v>
       </c>
       <c r="H61" s="75">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I61" s="153">
         <v>200</v>
       </c>
       <c r="J61" s="75">
+        <v>120</v>
+      </c>
+      <c r="K61" s="75">
+        <v>120</v>
+      </c>
+      <c r="L61" s="75">
         <v>200</v>
       </c>
-      <c r="K61" s="75">
-        <v>0</v>
-      </c>
-      <c r="L61" s="75">
-        <v>400</v>
-      </c>
       <c r="M61" s="152">
-        <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
-        <v>22</v>
+        <f t="shared" si="81"/>
+        <v>20</v>
       </c>
       <c r="N61" s="39">
         <f t="shared" si="18"/>
@@ -7337,12 +7349,12 @@
         <v>331.63</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P78" si="82">SUM(G61:I61)/20</f>
-        <v>14</v>
+        <f t="shared" si="82"/>
+        <v>18</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q78" si="83">SUM(J61:L61)/20</f>
-        <v>30</v>
+        <f t="shared" si="83"/>
+        <v>22</v>
       </c>
       <c r="R61" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7357,23 +7369,23 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U78" si="84">SUM(R61:T61)</f>
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V78" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" si="85"/>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W78" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X78" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y78" si="88">SUM(V61:X61)</f>
+        <f t="shared" si="88"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7382,35 +7394,35 @@
         <v>46192</v>
       </c>
       <c r="B62" s="47">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C62" s="151" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
       <c r="F62" s="75"/>
       <c r="G62" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H62" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I62" s="153">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J62" s="75">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="K62" s="75">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="L62" s="75">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="M62" s="152">
         <f t="shared" si="81"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N62" s="39">
         <f t="shared" si="18"/>
@@ -7422,11 +7434,11 @@
       </c>
       <c r="P62" s="73">
         <f t="shared" si="82"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Q62" s="40">
         <f t="shared" si="83"/>
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="R62" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7466,10 +7478,10 @@
         <v>46192</v>
       </c>
       <c r="B63" s="47">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C63" s="151" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
@@ -7550,10 +7562,10 @@
         <v>46192</v>
       </c>
       <c r="B64" s="47">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C64" s="151" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D64" s="75"/>
       <c r="E64" s="75"/>
@@ -7634,35 +7646,35 @@
         <v>46192</v>
       </c>
       <c r="B65" s="47">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C65" s="151" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D65" s="75"/>
       <c r="E65" s="75"/>
       <c r="F65" s="75"/>
       <c r="G65" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H65" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I65" s="153">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J65" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K65" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L65" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M65" s="152">
         <f t="shared" si="81"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N65" s="39">
         <f t="shared" si="18"/>
@@ -7674,11 +7686,11 @@
       </c>
       <c r="P65" s="73">
         <f t="shared" si="82"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q65" s="40">
         <f t="shared" si="83"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R65" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7718,35 +7730,35 @@
         <v>46192</v>
       </c>
       <c r="B66" s="47">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="151" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D66" s="75"/>
       <c r="E66" s="75"/>
       <c r="F66" s="75"/>
       <c r="G66" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H66" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I66" s="153">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J66" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K66" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L66" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M66" s="152">
         <f t="shared" si="81"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N66" s="39">
         <f t="shared" si="18"/>
@@ -7758,11 +7770,11 @@
       </c>
       <c r="P66" s="73">
         <f t="shared" si="82"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q66" s="40">
         <f t="shared" si="83"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R66" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7802,10 +7814,10 @@
         <v>46192</v>
       </c>
       <c r="B67" s="47">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C67" s="151" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D67" s="75"/>
       <c r="E67" s="75"/>
@@ -7886,35 +7898,35 @@
         <v>46192</v>
       </c>
       <c r="B68" s="47">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C68" s="151" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D68" s="75"/>
       <c r="E68" s="75"/>
       <c r="F68" s="75"/>
       <c r="G68" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H68" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I68" s="153">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J68" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K68" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L68" s="75">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M68" s="152">
         <f t="shared" si="81"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N68" s="39">
         <f t="shared" si="18"/>
@@ -7926,11 +7938,11 @@
       </c>
       <c r="P68" s="73">
         <f t="shared" si="82"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q68" s="40">
         <f t="shared" si="83"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R68" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7970,35 +7982,35 @@
         <v>46192</v>
       </c>
       <c r="B69" s="47">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C69" s="151" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
       <c r="G69" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H69" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I69" s="153">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J69" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K69" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L69" s="75">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M69" s="152">
         <f t="shared" si="81"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N69" s="39">
         <f t="shared" si="18"/>
@@ -8010,11 +8022,11 @@
       </c>
       <c r="P69" s="73">
         <f t="shared" si="82"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q69" s="40">
         <f t="shared" si="83"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R69" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8054,35 +8066,35 @@
         <v>46192</v>
       </c>
       <c r="B70" s="47">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C70" s="151" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
       <c r="G70" s="75">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H70" s="75">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I70" s="153">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J70" s="75">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K70" s="75">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L70" s="75">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M70" s="152">
         <f t="shared" si="81"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N70" s="39">
         <f t="shared" si="18"/>
@@ -8094,11 +8106,11 @@
       </c>
       <c r="P70" s="73">
         <f t="shared" si="82"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="40">
         <f t="shared" si="83"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R70" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8138,35 +8150,35 @@
         <v>46192</v>
       </c>
       <c r="B71" s="47">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C71" s="151" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
       <c r="G71" s="75">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H71" s="75">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I71" s="153">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J71" s="75">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K71" s="75">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L71" s="75">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M71" s="152">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N71" s="39">
         <f t="shared" si="18"/>
@@ -8178,11 +8190,11 @@
       </c>
       <c r="P71" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q71" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R71" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8222,10 +8234,10 @@
         <v>46192</v>
       </c>
       <c r="B72" s="47">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C72" s="151" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
@@ -8306,14 +8318,14 @@
         <v>46192</v>
       </c>
       <c r="B73" s="47">
-        <v>69</v>
-      </c>
-      <c r="C73" s="151" t="s">
-        <v>151</v>
+        <v>70</v>
+      </c>
+      <c r="C73" s="158" t="s">
+        <v>152</v>
       </c>
       <c r="D73" s="75"/>
       <c r="E73" s="75"/>
-      <c r="F73" s="75"/>
+      <c r="F73" s="50"/>
       <c r="G73" s="75">
         <v>40</v>
       </c>
@@ -8390,13 +8402,13 @@
         <v>46192</v>
       </c>
       <c r="B74" s="47">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="158" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D74" s="75"/>
-      <c r="E74" s="75"/>
+      <c r="E74" s="50"/>
       <c r="F74" s="50"/>
       <c r="G74" s="75">
         <v>40</v>
@@ -8474,10 +8486,10 @@
         <v>46192</v>
       </c>
       <c r="B75" s="47">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="158" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D75" s="75"/>
       <c r="E75" s="50"/>
@@ -8558,35 +8570,35 @@
         <v>46192</v>
       </c>
       <c r="B76" s="47">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C76" s="158" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D76" s="75"/>
       <c r="E76" s="50"/>
       <c r="F76" s="50"/>
-      <c r="G76" s="75">
-        <v>40</v>
-      </c>
-      <c r="H76" s="75">
-        <v>40</v>
-      </c>
-      <c r="I76" s="153">
-        <v>40</v>
-      </c>
-      <c r="J76" s="75">
-        <v>40</v>
-      </c>
-      <c r="K76" s="75">
-        <v>40</v>
-      </c>
-      <c r="L76" s="75">
-        <v>40</v>
+      <c r="G76" s="50">
+        <v>0</v>
+      </c>
+      <c r="H76" s="50">
+        <v>0</v>
+      </c>
+      <c r="I76" s="152">
+        <v>0</v>
+      </c>
+      <c r="J76" s="50">
+        <v>0</v>
+      </c>
+      <c r="K76" s="50">
+        <v>0</v>
+      </c>
+      <c r="L76" s="50">
+        <v>0</v>
       </c>
       <c r="M76" s="152">
         <f t="shared" si="81"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N76" s="39">
         <f t="shared" si="18"/>
@@ -8598,11 +8610,11 @@
       </c>
       <c r="P76" s="73">
         <f t="shared" si="82"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="40">
         <f t="shared" si="83"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R76" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8642,10 +8654,10 @@
         <v>46192</v>
       </c>
       <c r="B77" s="47">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C77" s="158" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D77" s="75"/>
       <c r="E77" s="50"/>
@@ -8722,39 +8734,37 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="78">
-        <v>46192</v>
-      </c>
+      <c r="A78" s="78"/>
       <c r="B78" s="47">
-        <v>74</v>
-      </c>
-      <c r="C78" s="158" t="s">
-        <v>156</v>
-      </c>
-      <c r="D78" s="75"/>
+        <v>75</v>
+      </c>
+      <c r="C78" s="151" t="s">
+        <v>163</v>
+      </c>
+      <c r="D78" s="50"/>
       <c r="E78" s="50"/>
       <c r="F78" s="50"/>
       <c r="G78" s="50">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="H78" s="50">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="I78" s="152">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="J78" s="50">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="K78" s="50">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="L78" s="50">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="M78" s="152">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>52.8</v>
       </c>
       <c r="N78" s="39">
         <f t="shared" si="18"/>
@@ -8765,12 +8775,12 @@
         <v>331.63</v>
       </c>
       <c r="P78" s="73">
-        <f t="shared" si="82"/>
-        <v>0</v>
+        <f t="shared" ref="P78:P82" si="89">SUM(G78:I78)/20</f>
+        <v>52.75</v>
       </c>
       <c r="Q78" s="40">
-        <f t="shared" si="83"/>
-        <v>0</v>
+        <f t="shared" ref="Q78:Q82" si="90">SUM(J78:L78)/20</f>
+        <v>52.85</v>
       </c>
       <c r="R78" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8785,58 +8795,60 @@
         <v>0</v>
       </c>
       <c r="U78" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" ref="U78:U82" si="91">SUM(R78:T78)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V78" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" ref="V78:V82" si="92">SUM(D78:F78)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W78" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" ref="W78:W82" si="93">SUM(G78:I78)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X78" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" ref="X78:X82" si="94">SUM(J78:L78)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y78" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="Y78:Y82" si="95">SUM(V78:X78)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="78"/>
       <c r="B79" s="47">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C79" s="151" t="s">
-        <v>163</v>
-      </c>
-      <c r="D79" s="50"/>
+        <v>164</v>
+      </c>
+      <c r="D79" s="50">
+        <v>40</v>
+      </c>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
       <c r="G79" s="50">
-        <v>314</v>
+        <v>40</v>
       </c>
       <c r="H79" s="50">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="I79" s="152">
-        <v>388</v>
+        <v>120</v>
       </c>
       <c r="J79" s="50">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="K79" s="50">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="L79" s="50">
-        <v>396</v>
+        <v>200</v>
       </c>
       <c r="M79" s="152">
         <f t="shared" si="81"/>
-        <v>52.8</v>
+        <v>15</v>
       </c>
       <c r="N79" s="39">
         <f t="shared" si="18"/>
@@ -8847,12 +8859,12 @@
         <v>331.63</v>
       </c>
       <c r="P79" s="73">
-        <f t="shared" ref="P79:P83" si="89">SUM(G79:I79)/20</f>
-        <v>52.75</v>
+        <f t="shared" si="89"/>
+        <v>8</v>
       </c>
       <c r="Q79" s="40">
-        <f t="shared" ref="Q79:Q83" si="90">SUM(J79:L79)/20</f>
-        <v>52.85</v>
+        <f t="shared" si="90"/>
+        <v>20</v>
       </c>
       <c r="R79" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8867,60 +8879,56 @@
         <v>0</v>
       </c>
       <c r="U79" s="53" t="e">
-        <f t="shared" ref="U79:U83" si="91">SUM(R79:T79)</f>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V79" s="54" t="e">
-        <f t="shared" ref="V79:V83" si="92">SUM(D79:F79)*$V$3</f>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W79" s="55">
-        <f t="shared" ref="W79:W83" si="93">SUM(G79:I79)*$W$3</f>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X79" s="55">
-        <f t="shared" ref="X79:X83" si="94">SUM(J79:L79)*$X$3</f>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y79" s="56" t="e">
-        <f t="shared" ref="Y79:Y83" si="95">SUM(V79:X79)</f>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="78"/>
       <c r="B80" s="47">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C80" s="151" t="s">
-        <v>164</v>
-      </c>
-      <c r="D80" s="50">
-        <v>40</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="D80" s="50"/>
       <c r="E80" s="50"/>
       <c r="F80" s="50"/>
       <c r="G80" s="50">
         <v>40</v>
       </c>
       <c r="H80" s="50">
-        <v>0</v>
-      </c>
-      <c r="I80" s="152">
-        <v>120</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I80" s="152"/>
       <c r="J80" s="50">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="K80" s="50">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L80" s="50">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="M80" s="152">
         <f t="shared" si="81"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N80" s="39">
         <f t="shared" si="18"/>
@@ -8932,11 +8940,11 @@
       </c>
       <c r="P80" s="73">
         <f t="shared" si="89"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q80" s="40">
         <f t="shared" si="90"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="R80" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8974,33 +8982,33 @@
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="78"/>
       <c r="B81" s="47">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C81" s="151" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D81" s="50"/>
       <c r="E81" s="50"/>
       <c r="F81" s="50"/>
       <c r="G81" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H81" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I81" s="152"/>
       <c r="J81" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K81" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L81" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M81" s="152">
         <f t="shared" si="81"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N81" s="39">
         <f t="shared" si="18"/>
@@ -9012,11 +9020,11 @@
       </c>
       <c r="P81" s="73">
         <f t="shared" si="89"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q81" s="40">
         <f t="shared" si="90"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R81" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9054,33 +9062,33 @@
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" s="78"/>
       <c r="B82" s="47">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C82" s="151" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D82" s="50"/>
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
       <c r="G82" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H82" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I82" s="152"/>
       <c r="J82" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K82" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L82" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M82" s="152">
         <f t="shared" si="81"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N82" s="39">
         <f t="shared" si="18"/>
@@ -9092,11 +9100,11 @@
       </c>
       <c r="P82" s="73">
         <f t="shared" si="89"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q82" s="40">
         <f t="shared" si="90"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R82" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9134,33 +9142,33 @@
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" s="78"/>
       <c r="B83" s="47">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C83" s="151" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D83" s="50"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
       <c r="G83" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H83" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I83" s="152"/>
       <c r="J83" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K83" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L83" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M83" s="152">
-        <f t="shared" si="81"/>
-        <v>5</v>
+        <f t="shared" ref="M83:M130" si="96">SUM(D83:L83)/40</f>
+        <v>10</v>
       </c>
       <c r="N83" s="39">
         <f t="shared" si="18"/>
@@ -9171,12 +9179,12 @@
         <v>331.63</v>
       </c>
       <c r="P83" s="73">
-        <f t="shared" si="89"/>
-        <v>4</v>
+        <f t="shared" ref="P83:P130" si="97">SUM(G83:I83)/20</f>
+        <v>8</v>
       </c>
       <c r="Q83" s="40">
-        <f t="shared" si="90"/>
-        <v>6</v>
+        <f t="shared" ref="Q83:Q130" si="98">SUM(J83:L83)/20</f>
+        <v>12</v>
       </c>
       <c r="R83" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9191,56 +9199,56 @@
         <v>0</v>
       </c>
       <c r="U83" s="53" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="U83:U130" si="99">SUM(R83:T83)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V83" s="54" t="e">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="V83:V130" si="100">SUM(D83:F83)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W83" s="55">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="W83:W130" si="101">SUM(G83:I83)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X83" s="55">
-        <f t="shared" si="94"/>
+        <f t="shared" ref="X83:X130" si="102">SUM(J83:L83)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y83" s="56" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="Y83:Y130" si="103">SUM(V83:X83)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="78"/>
       <c r="B84" s="47">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D84" s="50"/>
       <c r="E84" s="50"/>
       <c r="F84" s="50"/>
       <c r="G84" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H84" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I84" s="152"/>
       <c r="J84" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K84" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L84" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M84" s="152">
-        <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
-        <v>10</v>
+        <f t="shared" si="96"/>
+        <v>5</v>
       </c>
       <c r="N84" s="39">
         <f t="shared" si="18"/>
@@ -9251,12 +9259,12 @@
         <v>331.63</v>
       </c>
       <c r="P84" s="73">
-        <f t="shared" ref="P84:P131" si="97">SUM(G84:I84)/20</f>
-        <v>8</v>
+        <f t="shared" si="97"/>
+        <v>4</v>
       </c>
       <c r="Q84" s="40">
-        <f t="shared" ref="Q84:Q131" si="98">SUM(J84:L84)/20</f>
-        <v>12</v>
+        <f t="shared" si="98"/>
+        <v>6</v>
       </c>
       <c r="R84" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9271,33 +9279,33 @@
         <v>0</v>
       </c>
       <c r="U84" s="53" t="e">
-        <f t="shared" ref="U84:U131" si="99">SUM(R84:T84)</f>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="V84" s="54" t="e">
-        <f t="shared" ref="V84:V131" si="100">SUM(D84:F84)*$V$3</f>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="W84" s="55">
-        <f t="shared" ref="W84:W131" si="101">SUM(G84:I84)*$W$3</f>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="X84" s="55">
-        <f t="shared" ref="X84:X131" si="102">SUM(J84:L84)*$X$3</f>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="Y84" s="56" t="e">
-        <f t="shared" ref="Y84:Y131" si="103">SUM(V84:X84)</f>
+        <f t="shared" si="103"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="78"/>
       <c r="B85" s="47">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C85" s="151" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D85" s="50"/>
       <c r="E85" s="50"/>
@@ -9374,10 +9382,10 @@
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="78"/>
       <c r="B86" s="47">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C86" s="151" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D86" s="50"/>
       <c r="E86" s="50"/>
@@ -9454,10 +9462,10 @@
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="78"/>
       <c r="B87" s="47">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C87" s="151" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D87" s="50"/>
       <c r="E87" s="50"/>
@@ -9534,10 +9542,10 @@
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="78"/>
       <c r="B88" s="47">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C88" s="151" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D88" s="50"/>
       <c r="E88" s="50"/>
@@ -9614,10 +9622,10 @@
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="78"/>
       <c r="B89" s="47">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C89" s="151" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D89" s="50"/>
       <c r="E89" s="50"/>
@@ -9694,33 +9702,33 @@
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="78"/>
       <c r="B90" s="47">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C90" s="151" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D90" s="50"/>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
       <c r="G90" s="50">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H90" s="50">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="I90" s="152"/>
       <c r="J90" s="50">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="K90" s="50">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="L90" s="50">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="M90" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="N90" s="39">
         <f t="shared" si="18"/>
@@ -9732,11 +9740,11 @@
       </c>
       <c r="P90" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="Q90" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>27.3</v>
       </c>
       <c r="R90" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9774,33 +9782,35 @@
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="78"/>
       <c r="B91" s="47">
-        <v>87</v>
-      </c>
-      <c r="C91" s="151" t="s">
-        <v>168</v>
-      </c>
-      <c r="D91" s="50"/>
-      <c r="E91" s="50"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50">
-        <v>84</v>
-      </c>
-      <c r="H91" s="50">
-        <v>84</v>
-      </c>
-      <c r="I91" s="152"/>
-      <c r="J91" s="50">
-        <v>168</v>
-      </c>
-      <c r="K91" s="50">
-        <v>126</v>
-      </c>
-      <c r="L91" s="50">
-        <v>252</v>
+        <v>88</v>
+      </c>
+      <c r="C91" s="150" t="s">
+        <v>183</v>
+      </c>
+      <c r="D91" s="146">
+        <v>80</v>
+      </c>
+      <c r="E91" s="146"/>
+      <c r="F91" s="146"/>
+      <c r="G91" s="146">
+        <v>80</v>
+      </c>
+      <c r="H91" s="146">
+        <v>80</v>
+      </c>
+      <c r="I91" s="159"/>
+      <c r="J91" s="146">
+        <v>80</v>
+      </c>
+      <c r="K91" s="146">
+        <v>80</v>
+      </c>
+      <c r="L91" s="146">
+        <v>80</v>
       </c>
       <c r="M91" s="152">
         <f t="shared" si="96"/>
-        <v>17.850000000000001</v>
+        <v>12</v>
       </c>
       <c r="N91" s="39">
         <f t="shared" si="18"/>
@@ -9812,11 +9822,11 @@
       </c>
       <c r="P91" s="73">
         <f t="shared" si="97"/>
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Q91" s="40">
         <f t="shared" si="98"/>
-        <v>27.3</v>
+        <v>12</v>
       </c>
       <c r="R91" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9854,14 +9864,12 @@
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="78"/>
       <c r="B92" s="47">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C92" s="150" t="s">
-        <v>183</v>
-      </c>
-      <c r="D92" s="146">
-        <v>80</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="D92" s="146"/>
       <c r="E92" s="146"/>
       <c r="F92" s="146"/>
       <c r="G92" s="146">
@@ -9882,7 +9890,7 @@
       </c>
       <c r="M92" s="152">
         <f t="shared" si="96"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N92" s="39">
         <f t="shared" si="18"/>
@@ -9936,10 +9944,10 @@
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="78"/>
       <c r="B93" s="47">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C93" s="150" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D93" s="146"/>
       <c r="E93" s="146"/>
@@ -10016,33 +10024,29 @@
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="78"/>
       <c r="B94" s="47">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C94" s="150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D94" s="146"/>
       <c r="E94" s="146"/>
       <c r="F94" s="146"/>
-      <c r="G94" s="146">
-        <v>80</v>
-      </c>
-      <c r="H94" s="146">
-        <v>80</v>
-      </c>
+      <c r="G94" s="146"/>
+      <c r="H94" s="146"/>
       <c r="I94" s="159"/>
       <c r="J94" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K94" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L94" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M94" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N94" s="39">
         <f t="shared" si="18"/>
@@ -10054,11 +10058,11 @@
       </c>
       <c r="P94" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R94" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10096,29 +10100,33 @@
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="78"/>
       <c r="B95" s="47">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C95" s="150" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D95" s="146"/>
       <c r="E95" s="146"/>
       <c r="F95" s="146"/>
-      <c r="G95" s="146"/>
-      <c r="H95" s="146"/>
+      <c r="G95" s="146">
+        <v>80</v>
+      </c>
+      <c r="H95" s="146">
+        <v>80</v>
+      </c>
       <c r="I95" s="159"/>
       <c r="J95" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K95" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L95" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M95" s="152">
         <f t="shared" si="96"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N95" s="39">
         <f t="shared" si="18"/>
@@ -10130,11 +10138,11 @@
       </c>
       <c r="P95" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q95" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R95" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10172,33 +10180,33 @@
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="78"/>
       <c r="B96" s="47">
-        <v>92</v>
-      </c>
-      <c r="C96" s="150" t="s">
-        <v>166</v>
-      </c>
-      <c r="D96" s="146"/>
-      <c r="E96" s="146"/>
-      <c r="F96" s="146"/>
-      <c r="G96" s="146">
-        <v>80</v>
-      </c>
-      <c r="H96" s="146">
-        <v>80</v>
-      </c>
-      <c r="I96" s="159"/>
-      <c r="J96" s="146">
-        <v>80</v>
-      </c>
-      <c r="K96" s="146">
-        <v>80</v>
-      </c>
-      <c r="L96" s="146">
+        <v>93</v>
+      </c>
+      <c r="C96" s="164" t="s">
+        <v>181</v>
+      </c>
+      <c r="D96" s="165"/>
+      <c r="E96" s="165"/>
+      <c r="F96" s="165"/>
+      <c r="G96" s="165">
+        <v>80</v>
+      </c>
+      <c r="H96" s="165">
+        <v>80</v>
+      </c>
+      <c r="I96" s="166"/>
+      <c r="J96" s="165">
+        <v>80</v>
+      </c>
+      <c r="K96" s="165">
+        <v>120</v>
+      </c>
+      <c r="L96" s="165">
         <v>80</v>
       </c>
       <c r="M96" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N96" s="39">
         <f t="shared" si="18"/>
@@ -10214,7 +10222,7 @@
       </c>
       <c r="Q96" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R96" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10250,35 +10258,37 @@
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="78">
+        <v>46202</v>
+      </c>
       <c r="B97" s="47">
-        <v>93</v>
-      </c>
-      <c r="C97" s="164" t="s">
-        <v>181</v>
-      </c>
-      <c r="D97" s="165"/>
-      <c r="E97" s="165"/>
-      <c r="F97" s="165"/>
-      <c r="G97" s="165">
-        <v>80</v>
-      </c>
-      <c r="H97" s="165">
-        <v>80</v>
-      </c>
-      <c r="I97" s="166"/>
-      <c r="J97" s="165">
-        <v>80</v>
-      </c>
-      <c r="K97" s="165">
-        <v>120</v>
-      </c>
-      <c r="L97" s="165">
-        <v>80</v>
+        <v>94</v>
+      </c>
+      <c r="C97" s="151" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50">
+        <v>40</v>
+      </c>
+      <c r="H97" s="50">
+        <v>40</v>
+      </c>
+      <c r="I97" s="152"/>
+      <c r="J97" s="50">
+        <v>40</v>
+      </c>
+      <c r="K97" s="50">
+        <v>40</v>
+      </c>
+      <c r="L97" s="50">
+        <v>40</v>
       </c>
       <c r="M97" s="152">
         <f t="shared" si="96"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N97" s="39">
         <f t="shared" si="18"/>
@@ -10290,11 +10300,11 @@
       </c>
       <c r="P97" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q97" s="40">
         <f t="shared" si="98"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R97" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10334,33 +10344,33 @@
         <v>46202</v>
       </c>
       <c r="B98" s="47">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C98" s="151" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D98" s="50"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
       <c r="G98" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H98" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I98" s="152"/>
       <c r="J98" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K98" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L98" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M98" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N98" s="39">
         <f t="shared" si="18"/>
@@ -10372,11 +10382,11 @@
       </c>
       <c r="P98" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q98" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R98" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10416,33 +10426,23 @@
         <v>46202</v>
       </c>
       <c r="B99" s="47">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C99" s="151" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" s="50"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
-      <c r="G99" s="50">
-        <v>80</v>
-      </c>
-      <c r="H99" s="50">
-        <v>80</v>
-      </c>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
       <c r="I99" s="152"/>
-      <c r="J99" s="50">
-        <v>80</v>
-      </c>
-      <c r="K99" s="50">
-        <v>80</v>
-      </c>
-      <c r="L99" s="50">
-        <v>80</v>
-      </c>
+      <c r="J99" s="50"/>
+      <c r="K99" s="50"/>
+      <c r="L99" s="50"/>
       <c r="M99" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N99" s="39">
         <f t="shared" si="18"/>
@@ -10454,11 +10454,11 @@
       </c>
       <c r="P99" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R99" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10498,23 +10498,33 @@
         <v>46202</v>
       </c>
       <c r="B100" s="47">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C100" s="151" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D100" s="50"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
-      <c r="H100" s="50"/>
+      <c r="G100" s="50">
+        <v>40</v>
+      </c>
+      <c r="H100" s="50">
+        <v>40</v>
+      </c>
       <c r="I100" s="152"/>
-      <c r="J100" s="50"/>
-      <c r="K100" s="50"/>
-      <c r="L100" s="50"/>
+      <c r="J100" s="50">
+        <v>40</v>
+      </c>
+      <c r="K100" s="50">
+        <v>40</v>
+      </c>
+      <c r="L100" s="50">
+        <v>40</v>
+      </c>
       <c r="M100" s="152">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N100" s="39">
         <f t="shared" si="18"/>
@@ -10526,11 +10536,11 @@
       </c>
       <c r="P100" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q100" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R100" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10570,33 +10580,33 @@
         <v>46202</v>
       </c>
       <c r="B101" s="47">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C101" s="151" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D101" s="50"/>
       <c r="E101" s="50"/>
       <c r="F101" s="50"/>
       <c r="G101" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H101" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I101" s="152"/>
       <c r="J101" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K101" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L101" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M101" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N101" s="39">
         <f t="shared" si="18"/>
@@ -10608,11 +10618,11 @@
       </c>
       <c r="P101" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q101" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R101" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10652,33 +10662,33 @@
         <v>46202</v>
       </c>
       <c r="B102" s="47">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C102" s="151" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D102" s="50"/>
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
       <c r="G102" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H102" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I102" s="152"/>
       <c r="J102" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K102" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L102" s="50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M102" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N102" s="39">
         <f t="shared" si="18"/>
@@ -10690,11 +10700,11 @@
       </c>
       <c r="P102" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q102" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R102" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10734,10 +10744,10 @@
         <v>46202</v>
       </c>
       <c r="B103" s="47">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C103" s="151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D103" s="50"/>
       <c r="E103" s="50"/>
@@ -10816,10 +10826,10 @@
         <v>46202</v>
       </c>
       <c r="B104" s="47">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C104" s="151" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D104" s="50"/>
       <c r="E104" s="50"/>
@@ -10898,10 +10908,10 @@
         <v>46202</v>
       </c>
       <c r="B105" s="47">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C105" s="151" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D105" s="50"/>
       <c r="E105" s="50"/>
@@ -10980,10 +10990,10 @@
         <v>46202</v>
       </c>
       <c r="B106" s="47">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C106" s="151" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D106" s="50"/>
       <c r="E106" s="50"/>
@@ -11062,10 +11072,10 @@
         <v>46202</v>
       </c>
       <c r="B107" s="47">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C107" s="151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D107" s="50"/>
       <c r="E107" s="50"/>
@@ -11144,33 +11154,33 @@
         <v>46202</v>
       </c>
       <c r="B108" s="47">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C108" s="151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D108" s="50"/>
       <c r="E108" s="50"/>
       <c r="F108" s="50"/>
       <c r="G108" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H108" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I108" s="152"/>
       <c r="J108" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K108" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L108" s="50">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M108" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N108" s="39">
         <f t="shared" si="18"/>
@@ -11182,11 +11192,11 @@
       </c>
       <c r="P108" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q108" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R108" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11226,33 +11236,33 @@
         <v>46202</v>
       </c>
       <c r="B109" s="47">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C109" s="151" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="D109" s="50"/>
       <c r="E109" s="50"/>
       <c r="F109" s="50"/>
       <c r="G109" s="50">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="H109" s="50">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="I109" s="152"/>
       <c r="J109" s="50">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="K109" s="50">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="L109" s="50">
-        <v>80</v>
+        <v>520</v>
       </c>
       <c r="M109" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="N109" s="39">
         <f t="shared" si="18"/>
@@ -11264,11 +11274,11 @@
       </c>
       <c r="P109" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Q109" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="R109" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11308,33 +11318,29 @@
         <v>46202</v>
       </c>
       <c r="B110" s="47">
-        <v>106</v>
-      </c>
-      <c r="C110" s="151" t="s">
-        <v>25</v>
+        <v>107</v>
+      </c>
+      <c r="C110" s="169" t="s">
+        <v>205</v>
       </c>
       <c r="D110" s="50"/>
       <c r="E110" s="50"/>
       <c r="F110" s="50"/>
-      <c r="G110" s="50">
-        <v>160</v>
-      </c>
-      <c r="H110" s="50">
-        <v>280</v>
-      </c>
+      <c r="G110" s="50"/>
+      <c r="H110" s="50"/>
       <c r="I110" s="152"/>
       <c r="J110" s="50">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="K110" s="50">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="L110" s="50">
-        <v>520</v>
+        <v>120</v>
       </c>
       <c r="M110" s="152">
         <f t="shared" si="96"/>
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="N110" s="39">
         <f t="shared" si="18"/>
@@ -11346,11 +11352,11 @@
       </c>
       <c r="P110" s="73">
         <f t="shared" si="97"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="40">
         <f t="shared" si="98"/>
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="R110" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11390,29 +11396,33 @@
         <v>46202</v>
       </c>
       <c r="B111" s="47">
-        <v>107</v>
-      </c>
-      <c r="C111" s="151" t="s">
-        <v>205</v>
-      </c>
-      <c r="D111" s="50"/>
-      <c r="E111" s="50"/>
-      <c r="F111" s="50"/>
-      <c r="G111" s="50"/>
-      <c r="H111" s="50"/>
-      <c r="I111" s="152"/>
-      <c r="J111" s="50">
-        <v>40</v>
-      </c>
-      <c r="K111" s="50">
-        <v>40</v>
-      </c>
-      <c r="L111" s="50">
-        <v>120</v>
+        <v>108</v>
+      </c>
+      <c r="C111" s="164" t="s">
+        <v>206</v>
+      </c>
+      <c r="D111" s="165"/>
+      <c r="E111" s="165"/>
+      <c r="F111" s="165"/>
+      <c r="G111" s="165">
+        <v>80</v>
+      </c>
+      <c r="H111" s="165">
+        <v>40</v>
+      </c>
+      <c r="I111" s="166"/>
+      <c r="J111" s="165">
+        <v>80</v>
+      </c>
+      <c r="K111" s="165">
+        <v>40</v>
+      </c>
+      <c r="L111" s="165">
+        <v>80</v>
       </c>
       <c r="M111" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N111" s="39">
         <f t="shared" si="18"/>
@@ -11424,7 +11434,7 @@
       </c>
       <c r="P111" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q111" s="40">
         <f t="shared" si="98"/>
@@ -11465,36 +11475,36 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" s="78">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B112" s="47">
-        <v>108</v>
-      </c>
-      <c r="C112" s="164" t="s">
-        <v>206</v>
-      </c>
-      <c r="D112" s="165"/>
-      <c r="E112" s="165"/>
-      <c r="F112" s="165"/>
-      <c r="G112" s="165">
-        <v>80</v>
-      </c>
-      <c r="H112" s="165">
-        <v>40</v>
-      </c>
-      <c r="I112" s="166"/>
-      <c r="J112" s="165">
-        <v>80</v>
-      </c>
-      <c r="K112" s="165">
-        <v>40</v>
-      </c>
-      <c r="L112" s="165">
-        <v>80</v>
+        <v>109</v>
+      </c>
+      <c r="C112" s="150" t="s">
+        <v>207</v>
+      </c>
+      <c r="D112" s="146"/>
+      <c r="E112" s="146"/>
+      <c r="F112" s="146"/>
+      <c r="G112" s="146">
+        <v>40</v>
+      </c>
+      <c r="H112" s="146">
+        <v>40</v>
+      </c>
+      <c r="I112" s="159"/>
+      <c r="J112" s="146">
+        <v>40</v>
+      </c>
+      <c r="K112" s="146">
+        <v>40</v>
+      </c>
+      <c r="L112" s="146">
+        <v>40</v>
       </c>
       <c r="M112" s="152">
         <f t="shared" si="96"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N112" s="39">
         <f t="shared" si="18"/>
@@ -11506,11 +11516,11 @@
       </c>
       <c r="P112" s="73">
         <f t="shared" si="97"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q112" s="40">
         <f t="shared" si="98"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R112" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11550,33 +11560,33 @@
         <v>46203</v>
       </c>
       <c r="B113" s="47">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C113" s="150" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D113" s="146"/>
       <c r="E113" s="146"/>
       <c r="F113" s="146"/>
       <c r="G113" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H113" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I113" s="159"/>
       <c r="J113" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K113" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L113" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M113" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N113" s="39">
         <f t="shared" si="18"/>
@@ -11588,11 +11598,11 @@
       </c>
       <c r="P113" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q113" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R113" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11632,33 +11642,33 @@
         <v>46203</v>
       </c>
       <c r="B114" s="47">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C114" s="150" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D114" s="146"/>
       <c r="E114" s="146"/>
       <c r="F114" s="146"/>
       <c r="G114" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H114" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I114" s="159"/>
       <c r="J114" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K114" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L114" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M114" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N114" s="39">
         <f t="shared" si="18"/>
@@ -11670,11 +11680,11 @@
       </c>
       <c r="P114" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q114" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R114" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11714,10 +11724,10 @@
         <v>46203</v>
       </c>
       <c r="B115" s="47">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C115" s="150" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D115" s="146"/>
       <c r="E115" s="146"/>
@@ -11796,10 +11806,10 @@
         <v>46203</v>
       </c>
       <c r="B116" s="47">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C116" s="150" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D116" s="146"/>
       <c r="E116" s="146"/>
@@ -11878,10 +11888,10 @@
         <v>46203</v>
       </c>
       <c r="B117" s="47">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C117" s="150" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D117" s="146"/>
       <c r="E117" s="146"/>
@@ -11960,10 +11970,10 @@
         <v>46203</v>
       </c>
       <c r="B118" s="47">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C118" s="150" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D118" s="146"/>
       <c r="E118" s="146"/>
@@ -12042,10 +12052,10 @@
         <v>46203</v>
       </c>
       <c r="B119" s="47">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C119" s="150" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D119" s="146"/>
       <c r="E119" s="146"/>
@@ -12124,33 +12134,33 @@
         <v>46203</v>
       </c>
       <c r="B120" s="47">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C120" s="150" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D120" s="146"/>
       <c r="E120" s="146"/>
       <c r="F120" s="146"/>
       <c r="G120" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H120" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I120" s="159"/>
       <c r="J120" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K120" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L120" s="146">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M120" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N120" s="39">
         <f t="shared" si="18"/>
@@ -12162,11 +12172,11 @@
       </c>
       <c r="P120" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q120" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R120" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12206,33 +12216,33 @@
         <v>46203</v>
       </c>
       <c r="B121" s="47">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C121" s="150" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D121" s="146"/>
       <c r="E121" s="146"/>
       <c r="F121" s="146"/>
       <c r="G121" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H121" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I121" s="159"/>
       <c r="J121" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K121" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L121" s="146">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M121" s="152">
         <f t="shared" si="96"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N121" s="39">
         <f t="shared" si="18"/>
@@ -12244,11 +12254,11 @@
       </c>
       <c r="P121" s="73">
         <f t="shared" si="97"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q121" s="40">
         <f t="shared" si="98"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R121" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12288,10 +12298,10 @@
         <v>46203</v>
       </c>
       <c r="B122" s="47">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C122" s="150" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D122" s="146"/>
       <c r="E122" s="146"/>
@@ -12366,37 +12376,21 @@
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A123" s="78">
-        <v>46203</v>
-      </c>
-      <c r="B123" s="47">
-        <v>119</v>
-      </c>
-      <c r="C123" s="150" t="s">
-        <v>217</v>
-      </c>
-      <c r="D123" s="146"/>
-      <c r="E123" s="146"/>
-      <c r="F123" s="146"/>
-      <c r="G123" s="146">
-        <v>40</v>
-      </c>
-      <c r="H123" s="146">
-        <v>40</v>
-      </c>
-      <c r="I123" s="159"/>
-      <c r="J123" s="146">
-        <v>40</v>
-      </c>
-      <c r="K123" s="146">
-        <v>40</v>
-      </c>
-      <c r="L123" s="146">
-        <v>40</v>
-      </c>
+      <c r="A123" s="78"/>
+      <c r="B123" s="118"/>
+      <c r="C123" s="151"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="50"/>
+      <c r="G123" s="50"/>
+      <c r="H123" s="50"/>
+      <c r="I123" s="152"/>
+      <c r="J123" s="50"/>
+      <c r="K123" s="50"/>
+      <c r="L123" s="50"/>
       <c r="M123" s="152">
         <f t="shared" si="96"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N123" s="39">
         <f t="shared" si="18"/>
@@ -12408,11 +12402,11 @@
       </c>
       <c r="P123" s="73">
         <f t="shared" si="97"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="40">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R123" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12720,13 +12714,15 @@
       <c r="F128" s="50"/>
       <c r="G128" s="50"/>
       <c r="H128" s="50"/>
-      <c r="I128" s="152"/>
+      <c r="I128" s="152">
+        <v>17987</v>
+      </c>
       <c r="J128" s="50"/>
       <c r="K128" s="50"/>
       <c r="L128" s="50"/>
       <c r="M128" s="152">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>449.67500000000001</v>
       </c>
       <c r="N128" s="39">
         <f t="shared" si="18"/>
@@ -12738,7 +12734,7 @@
       </c>
       <c r="P128" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>899.35</v>
       </c>
       <c r="Q128" s="40">
         <f t="shared" si="98"/>
@@ -12786,15 +12782,13 @@
       <c r="F129" s="50"/>
       <c r="G129" s="50"/>
       <c r="H129" s="50"/>
-      <c r="I129" s="152">
-        <v>17987</v>
-      </c>
+      <c r="I129" s="152"/>
       <c r="J129" s="50"/>
       <c r="K129" s="50"/>
       <c r="L129" s="50"/>
       <c r="M129" s="152">
         <f t="shared" si="96"/>
-        <v>449.67500000000001</v>
+        <v>0</v>
       </c>
       <c r="N129" s="39">
         <f t="shared" si="18"/>
@@ -12806,7 +12800,7 @@
       </c>
       <c r="P129" s="73">
         <f t="shared" si="97"/>
-        <v>899.35</v>
+        <v>0</v>
       </c>
       <c r="Q129" s="40">
         <f t="shared" si="98"/>
@@ -12913,20 +12907,49 @@
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" s="78"/>
-      <c r="B131" s="118"/>
-      <c r="C131" s="151"/>
-      <c r="D131" s="50"/>
-      <c r="E131" s="50"/>
-      <c r="F131" s="50"/>
-      <c r="G131" s="50"/>
-      <c r="H131" s="50"/>
-      <c r="I131" s="152"/>
-      <c r="J131" s="50"/>
-      <c r="K131" s="50"/>
-      <c r="L131" s="50"/>
-      <c r="M131" s="152">
-        <f t="shared" si="96"/>
-        <v>0</v>
+      <c r="B131" s="180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" s="181"/>
+      <c r="D131" s="88">
+        <f>SUM(D6:D59)</f>
+        <v>1320</v>
+      </c>
+      <c r="E131" s="88">
+        <f>SUM(E6:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F131" s="88">
+        <f>SUM(F6:F59)</f>
+        <v>0</v>
+      </c>
+      <c r="G131" s="88">
+        <f>SUM(G6:G59)</f>
+        <v>7100</v>
+      </c>
+      <c r="H131" s="88">
+        <f>SUM(H6:H59)</f>
+        <v>7617</v>
+      </c>
+      <c r="I131" s="88">
+        <f>SUM(I6:I59)</f>
+        <v>10617</v>
+      </c>
+      <c r="J131" s="88">
+        <f>SUM(J6:J59)</f>
+        <v>11257</v>
+      </c>
+      <c r="K131" s="88">
+        <f>SUM(K6:K59)</f>
+        <v>9644</v>
+      </c>
+      <c r="L131" s="88">
+        <f>SUM(L6:L59)</f>
+        <v>13179</v>
+      </c>
+      <c r="M131" s="48">
+        <f t="shared" ref="M131:M134" si="104">SUM(D131:L131)/40</f>
+        <v>1518.35</v>
       </c>
       <c r="N131" s="39">
         <f t="shared" si="18"/>
@@ -12937,12 +12960,12 @@
         <v>331.63</v>
       </c>
       <c r="P131" s="73">
-        <f t="shared" si="97"/>
-        <v>0</v>
+        <f t="shared" ref="P131:P135" si="105">SUM(G131:I131)/20</f>
+        <v>1266.7</v>
       </c>
       <c r="Q131" s="40">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <f t="shared" ref="Q131:Q135" si="106">SUM(J131:L131)/20</f>
+        <v>1704</v>
       </c>
       <c r="R131" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12957,201 +12980,189 @@
         <v>0</v>
       </c>
       <c r="U131" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="V131" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" ref="V131:V135" si="107">SUM(D131:F131)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W131" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" ref="W131:W135" si="108">SUM(G131:I131)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X131" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" ref="X131:X135" si="109">SUM(J131:L131)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y131" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="192" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132" s="193"/>
-      <c r="D132" s="88">
-        <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>1320</v>
-      </c>
-      <c r="E132" s="88">
+      <c r="B132" s="118">
+        <v>0</v>
+      </c>
+      <c r="C132" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D132" s="119">
+        <v>1600</v>
+      </c>
+      <c r="E132" s="120"/>
+      <c r="F132" s="121"/>
+      <c r="G132" s="120"/>
+      <c r="H132" s="120"/>
+      <c r="I132" s="121"/>
+      <c r="J132" s="120">
+        <v>520</v>
+      </c>
+      <c r="K132" s="120">
+        <v>920</v>
+      </c>
+      <c r="L132" s="121">
+        <v>960</v>
+      </c>
+      <c r="M132" s="122">
+        <f>SUM(D132:L132)</f>
+        <v>4000</v>
+      </c>
+      <c r="N132" s="39"/>
+      <c r="O132" s="49"/>
+      <c r="P132" s="73"/>
+      <c r="Q132" s="40"/>
+      <c r="R132" s="51"/>
+      <c r="S132" s="52"/>
+      <c r="T132" s="52"/>
+      <c r="U132" s="53"/>
+      <c r="V132" s="54"/>
+      <c r="W132" s="55"/>
+      <c r="X132" s="55"/>
+      <c r="Y132" s="56"/>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A133" s="78"/>
+      <c r="B133" s="47">
+        <v>1</v>
+      </c>
+      <c r="C133" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D133" s="74"/>
+      <c r="E133" s="75"/>
+      <c r="F133" s="76"/>
+      <c r="G133" s="50">
+        <f>280+1600</f>
+        <v>1880</v>
+      </c>
+      <c r="H133" s="75">
+        <f>0+600</f>
+        <v>600</v>
+      </c>
+      <c r="I133" s="49">
+        <f>320+1800</f>
+        <v>2120</v>
+      </c>
+      <c r="J133" s="50">
+        <f>600+2800</f>
+        <v>3400</v>
+      </c>
+      <c r="K133" s="75">
+        <f>600+2400</f>
+        <v>3000</v>
+      </c>
+      <c r="L133" s="76">
+        <f>2200+2800</f>
+        <v>5000</v>
+      </c>
+      <c r="M133" s="48">
         <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="F132" s="88">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="G132" s="88">
-        <f t="shared" si="104"/>
-        <v>7140</v>
-      </c>
-      <c r="H132" s="88">
-        <f t="shared" si="104"/>
-        <v>7657</v>
-      </c>
-      <c r="I132" s="88">
-        <f t="shared" si="104"/>
-        <v>10657</v>
-      </c>
-      <c r="J132" s="88">
-        <f t="shared" si="104"/>
-        <v>11297</v>
-      </c>
-      <c r="K132" s="88">
-        <f t="shared" si="104"/>
-        <v>9684</v>
-      </c>
-      <c r="L132" s="88">
-        <f t="shared" si="104"/>
-        <v>13219</v>
-      </c>
-      <c r="M132" s="48">
-        <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>1524.35</v>
-      </c>
-      <c r="N132" s="39">
+        <v>400</v>
+      </c>
+      <c r="N133" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O132" s="49">
+      <c r="O133" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P132" s="73">
-        <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>1272.7</v>
-      </c>
-      <c r="Q132" s="40">
-        <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>1710</v>
-      </c>
-      <c r="R132" s="51" t="e">
+      <c r="P133" s="73">
+        <f t="shared" si="105"/>
+        <v>230</v>
+      </c>
+      <c r="Q133" s="40">
+        <f t="shared" si="106"/>
+        <v>570</v>
+      </c>
+      <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S132" s="52">
+      <c r="S133" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T132" s="52">
+      <c r="T133" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U132" s="53" t="e">
+      <c r="U133" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V132" s="54" t="e">
-        <f t="shared" ref="V132:V136" si="108">SUM(D132:F132)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W132" s="55">
-        <f t="shared" ref="W132:W136" si="109">SUM(G132:I132)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X132" s="55">
-        <f t="shared" ref="X132:X136" si="110">SUM(J132:L132)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y132" s="56" t="e">
-        <f t="shared" si="44"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A133" s="78"/>
-      <c r="B133" s="118">
-        <v>0</v>
-      </c>
-      <c r="C133" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D133" s="119">
-        <v>1600</v>
-      </c>
-      <c r="E133" s="120"/>
-      <c r="F133" s="121"/>
-      <c r="G133" s="120"/>
-      <c r="H133" s="120"/>
-      <c r="I133" s="121"/>
-      <c r="J133" s="120">
-        <v>520</v>
-      </c>
-      <c r="K133" s="120">
-        <v>920</v>
-      </c>
-      <c r="L133" s="121">
-        <v>960</v>
-      </c>
-      <c r="M133" s="122">
-        <f>SUM(D133:L133)</f>
-        <v>4000</v>
-      </c>
-      <c r="N133" s="39"/>
-      <c r="O133" s="49"/>
-      <c r="P133" s="73"/>
-      <c r="Q133" s="40"/>
-      <c r="R133" s="51"/>
-      <c r="S133" s="52"/>
-      <c r="T133" s="52"/>
-      <c r="U133" s="53"/>
-      <c r="V133" s="54"/>
-      <c r="W133" s="55"/>
-      <c r="X133" s="55"/>
-      <c r="Y133" s="56"/>
+      <c r="V133" s="54" t="e">
+        <f t="shared" si="107"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W133" s="55">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="X133" s="55">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="Y133" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A134" s="78"/>
       <c r="B134" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D134" s="74"/>
+        <v>27</v>
+      </c>
+      <c r="D134" s="74">
+        <v>1400</v>
+      </c>
       <c r="E134" s="75"/>
       <c r="F134" s="76"/>
       <c r="G134" s="50">
-        <f>280+1600</f>
-        <v>1880</v>
+        <v>400</v>
       </c>
       <c r="H134" s="75">
-        <f>0+600</f>
+        <v>400</v>
+      </c>
+      <c r="I134" s="49">
+        <v>0</v>
+      </c>
+      <c r="J134" s="50">
+        <v>400</v>
+      </c>
+      <c r="K134" s="75">
+        <v>400</v>
+      </c>
+      <c r="L134" s="76">
         <v>600</v>
       </c>
-      <c r="I134" s="49">
-        <f>320+1800</f>
-        <v>2120</v>
-      </c>
-      <c r="J134" s="50">
-        <f>600+2800</f>
-        <v>3400</v>
-      </c>
-      <c r="K134" s="75">
-        <f>600+2400</f>
-        <v>3000</v>
-      </c>
-      <c r="L134" s="76">
-        <f>2200+2800</f>
-        <v>5000</v>
-      </c>
       <c r="M134" s="48">
-        <f t="shared" si="105"/>
-        <v>400</v>
+        <f t="shared" si="104"/>
+        <v>90</v>
       </c>
       <c r="N134" s="39">
         <f t="shared" si="18"/>
@@ -13162,12 +13173,12 @@
         <v>331.63</v>
       </c>
       <c r="P134" s="73">
+        <f t="shared" si="105"/>
+        <v>40</v>
+      </c>
+      <c r="Q134" s="40">
         <f t="shared" si="106"/>
-        <v>230</v>
-      </c>
-      <c r="Q134" s="40">
-        <f t="shared" si="107"/>
-        <v>570</v>
+        <v>70</v>
       </c>
       <c r="R134" s="51" t="e">
         <f t="shared" si="4"/>
@@ -13186,15 +13197,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V134" s="54" t="e">
+        <f t="shared" si="107"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W134" s="55">
         <f t="shared" si="108"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W134" s="55">
+        <v>0</v>
+      </c>
+      <c r="X134" s="55">
         <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="X134" s="55">
-        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="Y134" s="56" t="e">
@@ -13202,55 +13213,66 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B135" s="47">
-        <v>2</v>
-      </c>
-      <c r="C135" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135" s="74">
+    <row r="135" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B135" s="193" t="s">
+        <v>93</v>
+      </c>
+      <c r="C135" s="194"/>
+      <c r="D135" s="87">
+        <f>SUM(D133:D134)</f>
         <v>1400</v>
       </c>
-      <c r="E135" s="75"/>
-      <c r="F135" s="76"/>
-      <c r="G135" s="50">
-        <v>400</v>
-      </c>
-      <c r="H135" s="75">
-        <v>400</v>
-      </c>
-      <c r="I135" s="49">
-        <v>0</v>
-      </c>
-      <c r="J135" s="50">
-        <v>400</v>
-      </c>
-      <c r="K135" s="75">
-        <v>400</v>
-      </c>
-      <c r="L135" s="76">
-        <v>600</v>
-      </c>
-      <c r="M135" s="48">
-        <f t="shared" si="105"/>
-        <v>90</v>
-      </c>
-      <c r="N135" s="39">
+      <c r="E135" s="87">
+        <f t="shared" ref="E135:L135" si="110">SUM(E133:E134)</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="87">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="G135" s="87">
+        <f t="shared" si="110"/>
+        <v>2280</v>
+      </c>
+      <c r="H135" s="87">
+        <f t="shared" si="110"/>
+        <v>1000</v>
+      </c>
+      <c r="I135" s="87">
+        <f t="shared" si="110"/>
+        <v>2120</v>
+      </c>
+      <c r="J135" s="87">
+        <f t="shared" si="110"/>
+        <v>3800</v>
+      </c>
+      <c r="K135" s="87">
+        <f t="shared" si="110"/>
+        <v>3400</v>
+      </c>
+      <c r="L135" s="87">
+        <f t="shared" si="110"/>
+        <v>5600</v>
+      </c>
+      <c r="M135" s="123">
+        <f>SUM(M132:M134)</f>
+        <v>4490</v>
+      </c>
+      <c r="N135" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O135" s="49">
+      <c r="O135" s="58">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
       <c r="P135" s="73">
+        <f t="shared" si="105"/>
+        <v>270</v>
+      </c>
+      <c r="Q135" s="40">
         <f t="shared" si="106"/>
-        <v>40</v>
-      </c>
-      <c r="Q135" s="40">
-        <f t="shared" si="107"/>
-        <v>70</v>
+        <v>640</v>
       </c>
       <c r="R135" s="51" t="e">
         <f t="shared" si="4"/>
@@ -13269,15 +13291,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V135" s="54" t="e">
+        <f t="shared" si="107"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W135" s="55">
         <f t="shared" si="108"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W135" s="55">
+        <v>0</v>
+      </c>
+      <c r="X135" s="55">
         <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="X135" s="55">
-        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="Y135" s="56" t="e">
@@ -13286,208 +13308,114 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="180" t="s">
-        <v>93</v>
-      </c>
-      <c r="C136" s="181"/>
-      <c r="D136" s="87">
-        <f>SUM(D134:D135)</f>
-        <v>1400</v>
-      </c>
-      <c r="E136" s="87">
-        <f t="shared" ref="E136:L136" si="111">SUM(E134:E135)</f>
-        <v>0</v>
-      </c>
-      <c r="F136" s="87">
+      <c r="B136" s="182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="183"/>
+      <c r="D136" s="89">
+        <f>SUM(D131,D135)</f>
+        <v>2720</v>
+      </c>
+      <c r="E136" s="89">
+        <f t="shared" ref="E136:L136" si="111">SUM(E131,E135)</f>
+        <v>0</v>
+      </c>
+      <c r="F136" s="89">
         <f t="shared" si="111"/>
         <v>0</v>
       </c>
-      <c r="G136" s="87">
+      <c r="G136" s="89">
         <f t="shared" si="111"/>
-        <v>2280</v>
-      </c>
-      <c r="H136" s="87">
+        <v>9380</v>
+      </c>
+      <c r="H136" s="89">
         <f t="shared" si="111"/>
-        <v>1000</v>
-      </c>
-      <c r="I136" s="87">
+        <v>8617</v>
+      </c>
+      <c r="I136" s="89">
         <f t="shared" si="111"/>
-        <v>2120</v>
-      </c>
-      <c r="J136" s="87">
+        <v>12737</v>
+      </c>
+      <c r="J136" s="89">
         <f t="shared" si="111"/>
-        <v>3800</v>
-      </c>
-      <c r="K136" s="87">
+        <v>15057</v>
+      </c>
+      <c r="K136" s="89">
         <f t="shared" si="111"/>
-        <v>3400</v>
-      </c>
-      <c r="L136" s="87">
+        <v>13044</v>
+      </c>
+      <c r="L136" s="89">
         <f t="shared" si="111"/>
-        <v>5600</v>
-      </c>
-      <c r="M136" s="123">
-        <f>SUM(M133:M135)</f>
-        <v>4490</v>
-      </c>
-      <c r="N136" s="59">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O136" s="58">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P136" s="73">
-        <f t="shared" si="106"/>
-        <v>270</v>
-      </c>
-      <c r="Q136" s="40">
-        <f t="shared" si="107"/>
-        <v>640</v>
-      </c>
-      <c r="R136" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S136" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T136" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U136" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V136" s="54" t="e">
-        <f t="shared" si="108"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W136" s="55">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="X136" s="55">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="Y136" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="169" t="s">
-        <v>11</v>
-      </c>
-      <c r="C137" s="170"/>
-      <c r="D137" s="89">
-        <f>SUM(D132,D136)</f>
-        <v>2720</v>
-      </c>
-      <c r="E137" s="89">
-        <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
-        <v>0</v>
-      </c>
-      <c r="F137" s="89">
+        <v>18779</v>
+      </c>
+      <c r="M136" s="60">
+        <f t="shared" si="0"/>
+        <v>2008.35</v>
+      </c>
+      <c r="N136" s="63">
+        <f>SUM(N5:N135)</f>
+        <v>0</v>
+      </c>
+      <c r="O136" s="61">
+        <f t="shared" ref="O136:Y136" si="112">SUM(O5:O135)</f>
+        <v>43111.899999999951</v>
+      </c>
+      <c r="P136" s="62">
         <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="G137" s="89">
+        <v>4642.45</v>
+      </c>
+      <c r="Q136" s="64">
         <f t="shared" si="112"/>
-        <v>9420</v>
-      </c>
-      <c r="H137" s="89">
+        <v>6003.25</v>
+      </c>
+      <c r="R136" s="65" t="e">
         <f t="shared" si="112"/>
-        <v>8657</v>
-      </c>
-      <c r="I137" s="89">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S136" s="66">
         <f t="shared" si="112"/>
-        <v>12777</v>
-      </c>
-      <c r="J137" s="89">
+        <v>0</v>
+      </c>
+      <c r="T136" s="66">
         <f t="shared" si="112"/>
-        <v>15097</v>
-      </c>
-      <c r="K137" s="89">
+        <v>0</v>
+      </c>
+      <c r="U136" s="67" t="e">
         <f t="shared" si="112"/>
-        <v>13084</v>
-      </c>
-      <c r="L137" s="89">
+        <v>#VALUE!</v>
+      </c>
+      <c r="V136" s="68" t="e">
         <f t="shared" si="112"/>
-        <v>18819</v>
-      </c>
-      <c r="M137" s="60">
-        <f t="shared" si="0"/>
-        <v>2014.35</v>
-      </c>
-      <c r="N137" s="63">
-        <f>SUM(N5:N136)</f>
-        <v>0</v>
-      </c>
-      <c r="O137" s="61">
-        <f t="shared" ref="O137:Y137" si="113">SUM(O5:O136)</f>
-        <v>43443.529999999948</v>
-      </c>
-      <c r="P137" s="62">
-        <f t="shared" si="113"/>
-        <v>4654.45</v>
-      </c>
-      <c r="Q137" s="64">
-        <f t="shared" si="113"/>
-        <v>6015.25</v>
-      </c>
-      <c r="R137" s="65" t="e">
-        <f t="shared" si="113"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S137" s="66">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="T137" s="66">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="U137" s="67" t="e">
-        <f t="shared" si="113"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V137" s="68" t="e">
-        <f t="shared" si="113"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W137" s="69">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="X137" s="69">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="Y137" s="70" t="e">
-        <f t="shared" si="113"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W136" s="69">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="X136" s="69">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="Y136" s="70" t="e">
+        <f t="shared" si="112"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B131:C131"/>
   </mergeCells>
-  <conditionalFormatting sqref="C45:C59">
+  <conditionalFormatting sqref="C44:C58">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13515,24 +13443,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="194" t="s">
+      <c r="C3" s="195" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="198" t="s">
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="199"/>
-      <c r="K3" s="200" t="s">
+      <c r="I3" s="200"/>
+      <c r="K3" s="201" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="200"/>
-      <c r="M3" s="200"/>
-      <c r="N3" s="200"/>
-      <c r="O3" s="200"/>
+      <c r="L3" s="201"/>
+      <c r="M3" s="201"/>
+      <c r="N3" s="201"/>
+      <c r="O3" s="201"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="109"/>
@@ -13744,14 +13672,14 @@
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="197" t="s">
+      <c r="C11" s="198" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="197"/>
-      <c r="F11" s="197" t="s">
+      <c r="D11" s="198"/>
+      <c r="F11" s="198" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="197"/>
+      <c r="G11" s="198"/>
       <c r="H11" t="s">
         <v>157</v>
       </c>
